--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20415"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/B2 - LZK-Rechner LNF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\Online-Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{91E35081-D1C7-4439-AB28-1F61A1A8072A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{563669AE-6969-42B3-916F-D46FD854E008}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57FFC95-8146-4260-848E-B11F6662749F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1160,9 +1160,6 @@
     </r>
   </si>
   <si>
-    <t>Ladeverhalten Elektroauto</t>
-  </si>
-  <si>
     <t>Ergänzende Angaben für Elektrofahrzeuge:</t>
   </si>
   <si>
@@ -3456,6 +3453,9 @@
   </si>
   <si>
     <t>=Input_Beschaffung!$C$14</t>
+  </si>
+  <si>
+    <t>Ladeverhalten Elektrofahrzeug</t>
   </si>
 </sst>
 </file>
@@ -5958,64 +5958,64 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6053,11 +6053,292 @@
   </cellStyles>
   <dxfs count="104">
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFB9DCFF"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB9DCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color auto="1"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -6254,6 +6535,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6560,294 +6848,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB9DCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -12699,8 +12699,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10145819" y="2392680"/>
-          <a:ext cx="1630074" cy="969010"/>
+          <a:off x="10143914" y="2432685"/>
+          <a:ext cx="1631979" cy="972820"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -14294,7 +14294,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -14304,7 +14304,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14327,7 +14327,7 @@
     </row>
     <row r="5" spans="2:10" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="391" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C5" s="391"/>
       <c r="D5" s="391"/>
@@ -14375,7 +14375,7 @@
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
       <c r="F9" s="392" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G9" s="392"/>
       <c r="H9" s="392"/>
@@ -14395,7 +14395,7 @@
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
       <c r="F11" s="393" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G11" s="394"/>
       <c r="H11" s="394"/>
@@ -14558,7 +14558,7 @@
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
       <c r="F28" s="401" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G28" s="401"/>
       <c r="H28" s="401"/>
@@ -14756,7 +14756,7 @@
     </row>
     <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="402" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C46" s="402"/>
       <c r="D46" s="402"/>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -14944,7 +14944,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -14960,7 +14960,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="54">
         <v>4</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter4=0,"",Anbieter4)</f>
@@ -14995,7 +14995,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15003,7 +15003,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller4=0,"",Hersteller4)</f>
@@ -15015,7 +15015,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell4=0,"",Modell4)</f>
@@ -15027,7 +15027,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo4=0,"",Zusatzinfo4)</f>
@@ -15039,7 +15039,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart4=0,"",Antriebsart4)</f>
@@ -15050,7 +15050,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie4=0,"",Energie4)</f>
@@ -15066,7 +15066,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15082,7 +15082,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
@@ -15094,35 +15094,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP4/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
@@ -15137,14 +15137,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -15157,7 +15157,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -15169,7 +15169,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -15182,7 +15182,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -15191,42 +15191,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,8,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -15239,7 +15239,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4)</f>
@@ -15251,70 +15251,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -15327,7 +15327,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4,IF(Antriebsart4="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15339,28 +15339,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15371,7 +15371,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15388,10 +15388,10 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
@@ -15402,14 +15402,14 @@
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
@@ -15422,21 +15422,21 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15460,20 +15460,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -15483,67 +15483,67 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="333" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="334" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="80" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
@@ -15599,14 +15599,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -15621,26 +15621,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -15654,7 +15654,7 @@
     <mergeCell ref="A60:A62"/>
   </mergeCells>
   <conditionalFormatting sqref="A16:D23">
-    <cfRule type="expression" dxfId="60" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>Antriebsart4&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15691,7 +15691,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15704,7 +15704,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -15720,7 +15720,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="54">
         <v>5</v>
@@ -15733,7 +15733,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter5=0,"",Anbieter5)</f>
@@ -15755,7 +15755,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15763,7 +15763,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller5=0,"",Hersteller5)</f>
@@ -15775,7 +15775,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell5=0,"",Modell5)</f>
@@ -15787,7 +15787,7 @@
     </row>
     <row r="12" spans="2:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo5=0,"",Zusatzinfo5)</f>
@@ -15799,7 +15799,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart5=0,"",Antriebsart5)</f>
@@ -15810,7 +15810,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie5=0,"",Energie5)</f>
@@ -15828,7 +15828,7 @@
     </row>
     <row r="16" spans="2:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15845,7 +15845,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
@@ -15857,35 +15857,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP5/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
@@ -15900,14 +15900,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -15920,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -15932,7 +15932,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -15945,7 +15945,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -15954,42 +15954,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,8,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -16002,7 +16002,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5)</f>
@@ -16015,70 +16015,70 @@
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A33" s="126"/>
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -16091,7 +16091,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5,IF(Antriebsart5="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -16103,28 +16103,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -16135,7 +16135,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -16152,10 +16152,10 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
@@ -16166,14 +16166,14 @@
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
@@ -16186,21 +16186,21 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -16224,20 +16224,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -16247,67 +16247,67 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="330" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
@@ -16363,14 +16363,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -16385,26 +16385,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -16418,7 +16418,7 @@
     <mergeCell ref="A60:A62"/>
   </mergeCells>
   <conditionalFormatting sqref="A16:D23">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>Antriebsart5&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16450,7 +16450,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H2" s="106" t="s">
         <v>20</v>
@@ -16458,7 +16458,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16467,18 +16467,18 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>163</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="302">
         <v>74.027000000000001</v>
@@ -16487,12 +16487,12 @@
         <v>23.4</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="302">
         <v>72.787000000000006</v>
@@ -16501,12 +16501,12 @@
         <v>23.2</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" s="302">
         <v>56.220999999999997</v>
@@ -16515,12 +16515,12 @@
         <v>20.3</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16530,7 +16530,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="154" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C12" s="93"/>
       <c r="D12" s="5"/>
@@ -16548,14 +16548,14 @@
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="110" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="472" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D14" s="472"/>
       <c r="E14" s="473" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F14" s="473"/>
       <c r="G14" s="304"/>
@@ -16563,40 +16563,40 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="58">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E15" s="136">
         <f>42.722*0.832</f>
         <v>35.544704000000003</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G15" s="111"/>
       <c r="H15" s="136"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" s="58">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E16" s="136">
         <f>43.543*0.742</f>
         <v>32.308906</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G16" s="111"/>
       <c r="H16" s="136"/>
@@ -16604,54 +16604,54 @@
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="66"/>
       <c r="B17" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="58">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E17" s="303">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="H20" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B21" s="66"/>
       <c r="I21" s="58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16661,13 +16661,13 @@
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B22" s="66"/>
       <c r="C22" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="D22" s="63" t="s">
-        <v>163</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
@@ -16675,7 +16675,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="58">
         <v>0</v>
@@ -16685,12 +16685,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="I23" s="58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J23" s="2">
         <v>2023</v>
@@ -16779,7 +16779,7 @@
     </row>
     <row r="24" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="96">
         <f>C7*E15</f>
@@ -16790,10 +16790,10 @@
         <v>831.74607360000005</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16882,7 +16882,7 @@
     </row>
     <row r="25" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="96">
         <f>C8*E16</f>
@@ -16893,12 +16893,12 @@
         <v>749.56661919999999</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C26" s="96">
         <f>C9*E17</f>
@@ -16909,7 +16909,7 @@
         <v>943.95</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K26" s="136"/>
     </row>
@@ -16964,7 +16964,7 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q2" s="106" t="s">
         <v>20</v>
@@ -16972,17 +16972,17 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="234" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16993,12 +16993,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -17008,39 +17008,39 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -17048,1231 +17048,1231 @@
         <v>28</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B193" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B194" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B195" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B196" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B197" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B198" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B199" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B200" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B201" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B202" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="203" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B203" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B204" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -18302,7 +18302,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -18314,37 +18314,37 @@
         <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -18353,7 +18353,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -18363,7 +18363,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -18372,22 +18372,22 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -18396,38 +18396,38 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -18436,39 +18436,39 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18477,17 +18477,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="5"/>
@@ -18496,32 +18496,32 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -18530,22 +18530,22 @@
     </row>
     <row r="41" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B41" s="385" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B42" s="385" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B43" s="385" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -18554,12 +18554,12 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -18585,7 +18585,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C2" s="132"/>
       <c r="E2" s="106" t="s">
@@ -18594,159 +18594,159 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C4" s="275" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C5" s="276" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>437</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="276" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="277" t="s">
+        <v>379</v>
+      </c>
+      <c r="C10" s="270" t="s">
         <v>380</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="270"/>
       <c r="C11" s="276" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="B12" s="278" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="275" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C13" s="276" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="278" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="275" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C17" s="276" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="275" t="s">
+        <v>386</v>
+      </c>
+      <c r="C20" s="275" t="s">
         <v>387</v>
-      </c>
-      <c r="C20" s="275" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="276" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>416</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>417</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C24" s="275" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C25" s="276" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18795,7 +18795,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>20</v>
@@ -18814,7 +18814,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C6" s="409"/>
       <c r="D6" s="410"/>
@@ -18885,7 +18885,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C13" s="406"/>
       <c r="D13" s="407"/>
@@ -18897,7 +18897,7 @@
     <row r="14" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="404"/>
       <c r="B14" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C14" s="406"/>
       <c r="D14" s="407"/>
@@ -18916,7 +18916,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C16" s="152"/>
       <c r="D16" s="55" t="s">
@@ -18956,7 +18956,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B20" s="298" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C20" s="151"/>
       <c r="D20" s="55"/>
@@ -19015,7 +19015,7 @@
         <v>33</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F27" s="274">
         <f>Grunddaten!G46</f>
@@ -19027,7 +19027,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" s="154" t="s">
-        <v>34</v>
+        <v>609</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -19051,17 +19051,17 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B31" s="170" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="I31" s="7"/>
       <c r="J31" s="146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
@@ -19073,14 +19073,14 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="171">
         <v>50</v>
       </c>
       <c r="D32" s="242"/>
       <c r="E32" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F32" s="172"/>
       <c r="G32" s="173"/>
@@ -19096,7 +19096,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="10">
         <f>100-J32</f>
@@ -19236,7 +19236,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -19257,7 +19257,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C4" s="155" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="156"/>
       <c r="E4" s="156"/>
@@ -19287,7 +19287,7 @@
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C6" s="88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="161">
@@ -19313,7 +19313,7 @@
     </row>
     <row r="7" spans="2:18" s="91" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="162" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="162"/>
       <c r="E7" s="139"/>
@@ -19333,7 +19333,7 @@
     </row>
     <row r="8" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="162" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="162"/>
       <c r="E8" s="139"/>
@@ -19356,7 +19356,7 @@
     </row>
     <row r="9" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="162" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="162"/>
       <c r="E9" s="140"/>
@@ -19376,7 +19376,7 @@
     </row>
     <row r="10" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="162" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140"/>
@@ -19387,7 +19387,7 @@
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="432" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M10" s="432"/>
       <c r="N10" s="236"/>
@@ -19398,7 +19398,7 @@
     </row>
     <row r="11" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C11" s="162" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141"/>
@@ -19408,7 +19408,7 @@
       <c r="I11" s="141"/>
       <c r="J11" s="238"/>
       <c r="K11" s="434" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L11" s="434"/>
       <c r="M11" s="434"/>
@@ -19420,7 +19420,7 @@
     </row>
     <row r="12" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="165" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141"/>
@@ -19430,7 +19430,7 @@
       <c r="I12" s="141"/>
       <c r="J12" s="164"/>
       <c r="K12" s="433" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L12" s="433"/>
       <c r="M12" s="433"/>
@@ -19442,7 +19442,7 @@
     </row>
     <row r="13" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="165" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D13" s="384"/>
       <c r="E13" s="139"/>
@@ -19486,10 +19486,10 @@
     </row>
     <row r="15" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="162" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="263" t="s">
         <v>57</v>
-      </c>
-      <c r="D15" s="263" t="s">
-        <v>58</v>
       </c>
       <c r="E15" s="361"/>
       <c r="F15" s="364"/>
@@ -19497,7 +19497,7 @@
       <c r="H15" s="361"/>
       <c r="I15" s="361"/>
       <c r="J15" s="264" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K15" s="164"/>
       <c r="L15" s="164"/>
@@ -19510,13 +19510,13 @@
     </row>
     <row r="16" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="431" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="429" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="D16" s="359" t="s">
         <v>61</v>
-      </c>
-      <c r="D16" s="359" t="s">
-        <v>62</v>
       </c>
       <c r="E16" s="365"/>
       <c r="F16" s="257"/>
@@ -19536,7 +19536,7 @@
       <c r="B17" s="431"/>
       <c r="C17" s="430"/>
       <c r="D17" s="166" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="357"/>
       <c r="F17" s="257"/>
@@ -19556,10 +19556,10 @@
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="431"/>
       <c r="C18" s="162" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="166" t="s">
         <v>64</v>
-      </c>
-      <c r="D18" s="166" t="s">
-        <v>65</v>
       </c>
       <c r="E18" s="258"/>
       <c r="F18" s="140"/>
@@ -19579,10 +19579,10 @@
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="431"/>
       <c r="C19" s="162" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="166" t="s">
         <v>66</v>
-      </c>
-      <c r="D19" s="166" t="s">
-        <v>67</v>
       </c>
       <c r="E19" s="258"/>
       <c r="F19" s="140"/>
@@ -19605,10 +19605,10 @@
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="431"/>
       <c r="C20" s="162" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="166" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" s="258"/>
       <c r="F20" s="140"/>
@@ -19628,10 +19628,10 @@
     <row r="21" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="431"/>
       <c r="C21" s="162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="166" t="s">
         <v>69</v>
-      </c>
-      <c r="D21" s="166" t="s">
-        <v>70</v>
       </c>
       <c r="E21" s="260"/>
       <c r="F21" s="261"/>
@@ -19650,10 +19650,10 @@
     </row>
     <row r="22" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C22" s="162" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="168" t="s">
         <v>71</v>
-      </c>
-      <c r="D22" s="168" t="s">
-        <v>72</v>
       </c>
       <c r="E22" s="257"/>
       <c r="F22" s="257"/>
@@ -19672,7 +19672,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D23" s="228" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" s="389">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
@@ -19705,7 +19705,7 @@
     </row>
     <row r="24" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C24" s="77" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D24" s="228"/>
       <c r="E24" s="389"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C25" s="331"/>
       <c r="D25" s="322" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E25" s="256"/>
       <c r="F25" s="256"/>
@@ -19742,7 +19742,7 @@
       <c r="B26" s="404"/>
       <c r="C26" s="331"/>
       <c r="D26" s="322" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E26" s="256"/>
       <c r="F26" s="256"/>
@@ -19759,7 +19759,7 @@
       <c r="B27" s="404"/>
       <c r="C27" s="335"/>
       <c r="D27" s="322" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E27" s="256"/>
       <c r="F27" s="256"/>
@@ -19774,7 +19774,7 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D28" s="228" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28" s="389">
         <f>IF(OR(AND(COUNT(E16:E22)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E17,E22)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E16,E18:E20)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
@@ -19807,7 +19807,7 @@
     </row>
     <row r="29" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="426" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F29" s="427"/>
       <c r="G29" s="427"/>
@@ -19816,7 +19816,7 @@
     </row>
     <row r="30" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E30" s="421" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F30" s="408"/>
       <c r="G30" s="408"/>
@@ -19832,7 +19832,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -19848,277 +19848,277 @@
     <mergeCell ref="B25:B27"/>
   </mergeCells>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="58" priority="21">
+    <cfRule type="expression" dxfId="98" priority="21">
       <formula>Antriebsart2="Verbrenner"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="95" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="95" operator="greaterThan">
       <formula>IF(Antriebsart2="Vollelektrisch (BEV)", IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxkWh_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxkWh_700kg, IF(Zuladung="700 - &lt;1000 kg", maxkWh_1000kg, maxkWh_größer1000kg))), IF(Antriebsart2="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_kWh, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17">
-    <cfRule type="expression" dxfId="56" priority="20">
+    <cfRule type="expression" dxfId="96" priority="20">
       <formula>Antriebsart3="Verbrenner"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="94" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="94" operator="greaterThan">
       <formula>IF(Antriebsart3="Vollelektrisch (BEV)", IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxkWh_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxkWh_700kg, IF(Zuladung="700 - &lt;1000 kg", maxkWh_1000kg, maxkWh_größer1000kg))), IF(Antriebsart3="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_kWh, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="54" priority="19">
+    <cfRule type="expression" dxfId="94" priority="19">
       <formula>Antriebsart4="Verbrenner"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="93" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="93" priority="93" operator="greaterThan">
       <formula>IF(Antriebsart4="Vollelektrisch (BEV)", IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxkWh_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxkWh_700kg, IF(Zuladung="700 - &lt;1000 kg", maxkWh_1000kg, maxkWh_größer1000kg))), IF(Antriebsart4="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_kWh, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="expression" dxfId="52" priority="18">
+    <cfRule type="expression" dxfId="92" priority="18">
       <formula>Antriebsart5="Verbrenner"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="45" operator="greaterThan">
       <formula>IF(Antriebsart5="Vollelektrisch (BEV)", IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxkWh_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxkWh_700kg, IF(Zuladung="700 - &lt;1000 kg", maxkWh_1000kg, maxkWh_größer1000kg))), IF(Antriebsart5="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_kWh, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F20">
-    <cfRule type="expression" dxfId="50" priority="15">
+    <cfRule type="expression" dxfId="90" priority="15">
       <formula>Antriebsart2="Vollelektrisch (BEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18:G20">
-    <cfRule type="expression" dxfId="49" priority="3">
+    <cfRule type="expression" dxfId="89" priority="3">
       <formula>Antriebsart3="Vollelektrisch (BEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H20">
-    <cfRule type="expression" dxfId="48" priority="2">
+    <cfRule type="expression" dxfId="88" priority="2">
       <formula>Antriebsart4="Vollelektrisch (BEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I20">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="87" priority="1">
       <formula>Antriebsart5="Vollelektrisch (BEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22">
-    <cfRule type="expression" dxfId="46" priority="77">
+    <cfRule type="expression" dxfId="86" priority="77">
       <formula>AND(Antriebsart2&lt;&gt;"Vollelektrisch (BEV)",Antriebsart2&lt;&gt;"Plug-In-Hybrid (PHEV)")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22">
-    <cfRule type="expression" dxfId="45" priority="76">
+    <cfRule type="expression" dxfId="85" priority="76">
       <formula>AND(Antriebsart3&lt;&gt;"Vollelektrisch (BEV)",Antriebsart3&lt;&gt;"Plug-In-Hybrid (PHEV)")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22">
-    <cfRule type="expression" dxfId="44" priority="75">
+    <cfRule type="expression" dxfId="84" priority="75">
       <formula>AND(Antriebsart4&lt;&gt;"Vollelektrisch (BEV)",Antriebsart4&lt;&gt;"Plug-In-Hybrid (PHEV)")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="expression" dxfId="43" priority="74">
+    <cfRule type="expression" dxfId="83" priority="74">
       <formula>AND(Antriebsart5&lt;&gt;"Vollelektrisch (BEV)",Antriebsart5&lt;&gt;"Plug-In-Hybrid (PHEV)")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15 F15:I15">
-    <cfRule type="expression" dxfId="42" priority="73">
+    <cfRule type="expression" dxfId="82" priority="73">
       <formula>FinArt&lt;&gt;"Leasing"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="41" priority="72">
+    <cfRule type="expression" dxfId="81" priority="72">
       <formula>FinArt="Leasing"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="expression" dxfId="40" priority="8">
+    <cfRule type="expression" dxfId="80" priority="8">
       <formula>Antriebsart2="Vollelektrisch (BEV)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="70" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="70" operator="greaterThan">
       <formula>IF(Antriebsart2="Verbrenner", max_Verbrauch_Verbrenner, IF(Antriebsart2="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_l, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16">
-    <cfRule type="expression" dxfId="38" priority="7">
+    <cfRule type="expression" dxfId="78" priority="7">
       <formula>Antriebsart3="Vollelektrisch (BEV)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="69" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="69" operator="greaterThan">
       <formula>IF(Antriebsart3="Verbrenner", max_Verbrauch_Verbrenner, IF(Antriebsart3="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_l, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="expression" dxfId="36" priority="6">
+    <cfRule type="expression" dxfId="76" priority="6">
       <formula>Antriebsart4="Vollelektrisch (BEV)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="75" priority="68" operator="greaterThan">
       <formula>IF(Antriebsart4="Verbrenner", max_Verbrauch_Verbrenner, IF(Antriebsart4="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_l, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="expression" dxfId="34" priority="10">
+    <cfRule type="expression" dxfId="74" priority="10">
       <formula>Antriebsart5="Vollelektrisch (BEV)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="67" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="73" priority="67" operator="greaterThan">
       <formula>IF(Antriebsart5="Verbrenner", max_Verbrauch_Verbrenner, IF(Antriebsart5="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_l, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="expression" dxfId="32" priority="58">
+    <cfRule type="expression" dxfId="72" priority="58">
       <formula>Antriebsart2&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21">
-    <cfRule type="expression" dxfId="31" priority="57">
+    <cfRule type="expression" dxfId="71" priority="57">
       <formula>Antriebsart3&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21">
-    <cfRule type="expression" dxfId="30" priority="56">
+    <cfRule type="expression" dxfId="70" priority="56">
       <formula>Antriebsart4&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="expression" dxfId="29" priority="48">
+    <cfRule type="expression" dxfId="69" priority="48">
       <formula>Antriebsart5&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18">
-    <cfRule type="cellIs" dxfId="28" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="82" operator="greaterThan">
       <formula>IF(Antriebsart4="Plug-in-Hybrid (PHEV)", maxCO2PHEV, IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxCO2_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxCO2_700kg, IF(Zuladung="700 - &lt;1000 kg", maxCO2_1000kg, IF(Zuladung="1000 - &lt;1300 kg", maxCO2_1300kg, maxCO2_größer1300kg)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="cellIs" dxfId="27" priority="81" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="81" operator="greaterThan">
       <formula>IF(Fahrzeugklasse2=N1I, maxNOX_N1I, IF(Fahrzeugklasse2=N1II, maxNOX_N1II, maxNOX_N1III))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:I20">
-    <cfRule type="cellIs" dxfId="26" priority="80" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="80" operator="greaterThan">
       <formula>maxPM</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:I21">
-    <cfRule type="cellIs" dxfId="0" priority="60" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="60" operator="lessThan">
       <formula>IF(AND(ISNUMBER(minReichwPHEV), ISBLANK(ReichwPHEV5)=FALSE), minReichwPHEV, 0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:I8">
-    <cfRule type="expression" dxfId="25" priority="39">
+    <cfRule type="expression" dxfId="64" priority="39">
       <formula>F$23=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:O8">
-    <cfRule type="expression" dxfId="24" priority="38">
+    <cfRule type="expression" dxfId="63" priority="38">
       <formula>$J$23=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:O19">
-    <cfRule type="expression" dxfId="23" priority="37">
+    <cfRule type="expression" dxfId="62" priority="37">
       <formula>AND($J$23=0,$J$28=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" dxfId="22" priority="35">
+    <cfRule type="expression" dxfId="61" priority="35">
       <formula>Antriebsart1="Verbrenner"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="98" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="98" operator="greaterThan">
       <formula>IF(Antriebsart1="Vollelektrisch (BEV)", IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxkWh_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxkWh_700kg, IF(Zuladung="700 - &lt;1000 kg", maxkWh_1000kg, maxkWh_größer1000kg))), IF(Antriebsart1="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_kWh, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E20">
-    <cfRule type="expression" dxfId="20" priority="26">
+    <cfRule type="expression" dxfId="59" priority="26">
       <formula>Antriebsart1="Vollelektrisch (BEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="expression" dxfId="19" priority="31">
+    <cfRule type="expression" dxfId="58" priority="31">
       <formula>AND(Antriebsart1&lt;&gt;"Vollelektrisch (BEV)",Antriebsart1&lt;&gt;"Plug-In-Hybrid (PHEV)")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="expression" dxfId="18" priority="30">
+    <cfRule type="expression" dxfId="57" priority="30">
       <formula>FinArt&lt;&gt;"Leasing"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="expression" dxfId="17" priority="9">
+    <cfRule type="expression" dxfId="56" priority="9">
       <formula>Antriebsart1="Vollelektrisch (BEV)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="29" operator="greaterThan">
       <formula>IF(Antriebsart1="Verbrenner", max_Verbrauch_Verbrenner, IF(Antriebsart1="Plug-in-Hybrid (PHEV)", max_Verbrauch_PHEV_l, 1000))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="expression" dxfId="15" priority="27">
+    <cfRule type="expression" dxfId="54" priority="27">
       <formula>Antriebsart1&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18">
-    <cfRule type="cellIs" dxfId="14" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="34" operator="greaterThan">
       <formula>IF(Antriebsart1="Plug-in-Hybrid (PHEV)", maxCO2PHEV, IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxCO2_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxCO2_700kg, IF(Zuladung="700 - &lt;1000 kg", maxCO2_1000kg, IF(Zuladung="1000 - &lt;1300 kg", maxCO2_1300kg, maxCO2_größer1300kg)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="cellIs" dxfId="13" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="33" operator="greaterThan">
       <formula>IF(Fahrzeugklasse1=N1I, maxNOX_N1I, IF(Fahrzeugklasse1=N1II, maxNOX_N1II, maxNOX_N1III))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="cellIs" dxfId="12" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="32" operator="greaterThan">
       <formula>maxPM</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="11" priority="25">
+    <cfRule type="expression" dxfId="50" priority="25">
       <formula>E$23=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D14">
-    <cfRule type="expression" dxfId="10" priority="22">
+    <cfRule type="expression" dxfId="49" priority="22">
       <formula>ISBLANK(FinArt)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18">
-    <cfRule type="cellIs" dxfId="9" priority="49" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="49" operator="greaterThan">
       <formula>IF(Antriebsart5="Plug-in-Hybrid (PHEV)", maxCO2PHEV, IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxCO2_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxCO2_700kg, IF(Zuladung="700 - &lt;1000 kg", maxCO2_1000kg, IF(Zuladung="1000 - &lt;1300 kg", maxCO2_1300kg, maxCO2_größer1300kg)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18">
-    <cfRule type="cellIs" dxfId="8" priority="51" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="51" operator="greaterThan">
       <formula>IF(Antriebsart3="Plug-in-Hybrid (PHEV)", maxCO2PHEV, IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxCO2_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxCO2_700kg, IF(Zuladung="700 - &lt;1000 kg", maxCO2_1000kg, IF(Zuladung="1000 - &lt;1300 kg", maxCO2_1300kg, maxCO2_größer1300kg)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="7" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="54" operator="greaterThan">
       <formula>IF(Antriebsart2="Plug-in-Hybrid (PHEV)", maxCO2PHEV, IF(Laderaum="Höhe ≥ 1,4 m oder Länge ≥ 3,0 m", maxCO2_Laderaum, IF(OR(Zuladung="&lt;700 kg", Zuladung="keine Anforderung"), maxCO2_700kg, IF(Zuladung="700 - &lt;1000 kg", maxCO2_1000kg, IF(Zuladung="1000 - &lt;1300 kg", maxCO2_1300kg, maxCO2_größer1300kg)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:I25">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="45" priority="14">
       <formula>ISBLANK($C$25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:I26">
-    <cfRule type="expression" dxfId="5" priority="12">
+    <cfRule type="expression" dxfId="44" priority="12">
       <formula>ISBLANK($C$26)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:I27">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="43" priority="11">
       <formula>ISBLANK($C$27)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="3" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="16" operator="greaterThan">
       <formula>IF(Fahrzeugklasse3=N1I, maxNOX_N1I, IF(Fahrzeugklasse3=N1II, maxNOX_N1II, maxNOX_N1III))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="cellIs" dxfId="2" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="50" operator="greaterThan">
       <formula>IF(Fahrzeugklasse4=N1I, maxNOX_N1I, IF(Fahrzeugklasse4=N1II, maxNOX_N1II, maxNOX_N1III))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19">
-    <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="greaterThan">
       <formula>IF(Fahrzeugklasse5=N1I, maxNOX_N1I, IF(Fahrzeugklasse5=N1II, maxNOX_N1II, maxNOX_N1III))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20225,7 +20225,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20239,7 +20239,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20267,7 +20267,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -20282,7 +20282,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20364,7 +20364,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20404,7 +20404,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20416,7 +20416,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -20463,10 +20463,10 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="177" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="178" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="179" t="str">
         <f>IF(FinArt="Kauf",Gesamtpreis1,"")</f>
@@ -20499,7 +20499,7 @@
         <v>Fahrzeugkosten (Leasingrate/Miete)</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" s="41">
         <f>Erg.Fzg._1!$C$54+Erg.Fzg._1!$C$55</f>
@@ -20525,10 +20525,10 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="336"/>
       <c r="B20" s="45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="41">
         <f>Erg.Fzg._1!$C$56</f>
@@ -20556,10 +20556,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="43">
         <f>Erg.Fzg._1!$C$57</f>
@@ -20585,10 +20585,10 @@
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="437"/>
       <c r="B22" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20615,10 +20615,10 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="438"/>
       <c r="B23" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="325" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="326" t="e">
         <f>Erg.Fzg._1!$C$59</f>
@@ -20740,10 +20740,10 @@
     <row r="27" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" s="51" t="e">
         <f>IF(SUM(D19:D26)=0,"",SUM(D19:D26))</f>
@@ -20769,7 +20769,7 @@
     <row r="28" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="50"/>
       <c r="D28" s="51" t="str">
@@ -20797,10 +20797,10 @@
     <row r="29" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D29" s="231">
         <f>IF(AND(COUNTIF(D19:D23,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D19:D23,0)&gt;1,Antriebsart1&lt;&gt;0),1,0))</f>
@@ -20830,10 +20830,10 @@
     <row r="30" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="316" t="s">
         <v>87</v>
-      </c>
-      <c r="C30" s="316" t="s">
-        <v>88</v>
       </c>
       <c r="D30" s="314" t="e">
         <f>Erg.Fzg._1!$C$65</f>
@@ -20859,10 +20859,10 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C31" s="317" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D31" s="318">
         <f>Erg.Fzg._1!$C$66</f>
@@ -20889,10 +20889,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D32" s="312" t="e">
         <f>SUM(D30:D31)</f>
@@ -20918,7 +20918,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="293" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -20992,33 +20992,33 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:H18">
-    <cfRule type="expression" dxfId="98" priority="20">
+    <cfRule type="expression" dxfId="39" priority="20">
       <formula>AND(KaufpreisRech="Wertminderung",FinArt="Kauf")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="97" priority="16">
+    <cfRule type="expression" dxfId="38" priority="16">
       <formula>"ISTLEER(Gesamtpreis3)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G2">
-    <cfRule type="expression" dxfId="96" priority="11">
+    <cfRule type="expression" dxfId="37" priority="11">
       <formula>$I$29=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:D36 F36:G36">
-    <cfRule type="top10" dxfId="95" priority="80" percent="1" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="94" priority="81" percent="1" rank="10"/>
-    <cfRule type="aboveAverage" dxfId="93" priority="82"/>
-    <cfRule type="aboveAverage" dxfId="92" priority="83" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="91" priority="84" equalAverage="1"/>
+    <cfRule type="top10" dxfId="36" priority="80" percent="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="35" priority="81" percent="1" rank="10"/>
+    <cfRule type="aboveAverage" dxfId="34" priority="82"/>
+    <cfRule type="aboveAverage" dxfId="33" priority="83" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="32" priority="84" equalAverage="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="top10" dxfId="90" priority="1" percent="1" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="89" priority="2" percent="1" rank="10"/>
-    <cfRule type="aboveAverage" dxfId="88" priority="3"/>
-    <cfRule type="aboveAverage" dxfId="87" priority="4" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="86" priority="5" equalAverage="1"/>
+    <cfRule type="top10" dxfId="31" priority="1" percent="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="30" priority="2" percent="1" rank="10"/>
+    <cfRule type="aboveAverage" dxfId="29" priority="3"/>
+    <cfRule type="aboveAverage" dxfId="28" priority="4" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="27" priority="5" equalAverage="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="J2" location="Anleitung!A1" display="zurück zu &quot;Anleitung&quot;" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -21049,7 +21049,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -21063,7 +21063,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -21091,7 +21091,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -21106,7 +21106,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -21188,7 +21188,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21228,7 +21228,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21240,7 +21240,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -21289,10 +21289,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="43">
         <f>Erg.Fzg._1!$C$57-D19</f>
@@ -21318,10 +21318,10 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="437"/>
       <c r="B19" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" s="43">
         <f>(Erg.Fzg._1!$C$35+Erg.Fzg._1!$C$36)*Haltedauer</f>
@@ -21347,10 +21347,10 @@
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="437"/>
       <c r="B20" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -21377,10 +21377,10 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="437"/>
       <c r="B21" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="47" t="e">
         <f>Erg.Fzg._1!$C$59</f>
@@ -21406,10 +21406,10 @@
     <row r="22" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18"/>
       <c r="B22" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="51" t="e">
         <f>IF(SUM(D18:D21)=0,"",SUM(D18:D21))</f>
@@ -21435,7 +21435,7 @@
     <row r="23" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="51" t="str">
@@ -21463,10 +21463,10 @@
     <row r="24" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" s="231">
         <f>IF(AND(COUNTIF(D18:D21,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D18:D21,0)&gt;1,Antriebsart1="Verbrenner"),1,IF(AND(COUNTIF(D18:D21,0)&gt;2,Antriebsart1&lt;&gt;""),1,0)))</f>
@@ -21496,10 +21496,10 @@
     <row r="25" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>87</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>88</v>
       </c>
       <c r="D25" s="32" t="e">
         <f>Erg.Fzg._1!$C$65</f>
@@ -21525,10 +21525,10 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" s="35">
         <f>Erg.Fzg._1!$C$66</f>
@@ -21555,10 +21555,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D27" s="312" t="e">
         <f>SUM(D25:D26)</f>
@@ -21584,7 +21584,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21646,7 +21646,7 @@
     <mergeCell ref="C6:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="D17:H17">
-    <cfRule type="cellIs" dxfId="85" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21663,23 +21663,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G2">
-    <cfRule type="expression" dxfId="84" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>$I$24=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:D31 F31:G31">
-    <cfRule type="top10" dxfId="83" priority="6" percent="1" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="82" priority="7" percent="1" rank="10"/>
-    <cfRule type="aboveAverage" dxfId="81" priority="8"/>
-    <cfRule type="aboveAverage" dxfId="80" priority="9" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="79" priority="10" equalAverage="1"/>
+    <cfRule type="top10" dxfId="24" priority="6" percent="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="23" priority="7" percent="1" rank="10"/>
+    <cfRule type="aboveAverage" dxfId="22" priority="8"/>
+    <cfRule type="aboveAverage" dxfId="21" priority="9" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="20" priority="10" equalAverage="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="top10" dxfId="78" priority="1" percent="1" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="77" priority="2" percent="1" rank="10"/>
-    <cfRule type="aboveAverage" dxfId="76" priority="3"/>
-    <cfRule type="aboveAverage" dxfId="75" priority="4" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="74" priority="5" equalAverage="1"/>
+    <cfRule type="top10" dxfId="19" priority="1" percent="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="18" priority="2" percent="1" rank="10"/>
+    <cfRule type="aboveAverage" dxfId="17" priority="3"/>
+    <cfRule type="aboveAverage" dxfId="16" priority="4" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="15" priority="5" equalAverage="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="J2" location="Anleitung!A1" display="zurück zu &quot;Anleitung&quot;" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21723,7 +21723,7 @@
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="119"/>
       <c r="B2" s="189" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
@@ -21752,7 +21752,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21776,448 +21776,448 @@
       <c r="H5" s="219"/>
       <c r="I5" s="190"/>
       <c r="J5" s="119"/>
-      <c r="L5" s="450" t="s">
-        <v>400</v>
-      </c>
-      <c r="M5" s="450"/>
-      <c r="N5" s="450"/>
+      <c r="L5" s="448" t="s">
+        <v>399</v>
+      </c>
+      <c r="M5" s="448"/>
+      <c r="N5" s="448"/>
     </row>
     <row r="6" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A6" s="404"/>
       <c r="B6" s="220" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="220" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="221" t="s">
+        <v>510</v>
+      </c>
+      <c r="E6" s="221" t="s">
+        <v>511</v>
+      </c>
+      <c r="F6" s="221" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="220" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="221" t="s">
-        <v>511</v>
-      </c>
-      <c r="E6" s="221" t="s">
-        <v>512</v>
-      </c>
-      <c r="F6" s="221" t="s">
+      <c r="G6" s="226" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="226" t="s">
+      <c r="H6" s="221" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="221" t="s">
+      <c r="I6" s="306" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="306" t="s">
-        <v>98</v>
-      </c>
       <c r="J6" s="119"/>
-      <c r="L6" s="450"/>
-      <c r="M6" s="450"/>
-      <c r="N6" s="450"/>
+      <c r="L6" s="448"/>
+      <c r="M6" s="448"/>
+      <c r="N6" s="448"/>
     </row>
     <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="352"/>
-      <c r="B7" s="451" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="460" t="s">
-        <v>45</v>
+      <c r="B7" s="449" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="452" t="s">
+        <v>44</v>
       </c>
       <c r="D7" s="370" t="s">
+        <v>512</v>
+      </c>
+      <c r="E7" s="386" t="s">
         <v>513</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>514</v>
       </c>
       <c r="F7" s="223">
         <v>230</v>
       </c>
       <c r="G7" s="272"/>
       <c r="H7" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I7" s="307">
         <f t="shared" ref="I7:I25" si="0">IF(ISBLANK(G7),F7,G7)</f>
         <v>230</v>
       </c>
       <c r="J7" s="119"/>
-      <c r="L7" s="450"/>
-      <c r="M7" s="450"/>
-      <c r="N7" s="450"/>
+      <c r="L7" s="448"/>
+      <c r="M7" s="448"/>
+      <c r="N7" s="448"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="352"/>
-      <c r="B8" s="452"/>
-      <c r="C8" s="461"/>
-      <c r="D8" s="463" t="s">
-        <v>515</v>
+      <c r="B8" s="450"/>
+      <c r="C8" s="453"/>
+      <c r="D8" s="455" t="s">
+        <v>514</v>
       </c>
       <c r="E8" s="387" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F8" s="223">
         <v>150</v>
       </c>
       <c r="G8" s="272"/>
       <c r="H8" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I8" s="307">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="J8" s="119"/>
-      <c r="L8" s="450"/>
-      <c r="M8" s="450"/>
-      <c r="N8" s="450"/>
+      <c r="L8" s="448"/>
+      <c r="M8" s="448"/>
+      <c r="N8" s="448"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="352"/>
-      <c r="B9" s="452"/>
-      <c r="C9" s="461"/>
-      <c r="D9" s="463"/>
+      <c r="B9" s="450"/>
+      <c r="C9" s="453"/>
+      <c r="D9" s="455"/>
       <c r="E9" s="386" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F9" s="223">
         <v>160</v>
       </c>
       <c r="G9" s="272"/>
       <c r="H9" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I9" s="307">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="J9" s="119"/>
-      <c r="L9" s="450"/>
-      <c r="M9" s="450"/>
-      <c r="N9" s="450"/>
+      <c r="L9" s="448"/>
+      <c r="M9" s="448"/>
+      <c r="N9" s="448"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="352"/>
-      <c r="B10" s="452"/>
-      <c r="C10" s="461"/>
-      <c r="D10" s="463"/>
+      <c r="B10" s="450"/>
+      <c r="C10" s="453"/>
+      <c r="D10" s="455"/>
       <c r="E10" s="387" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F10" s="223">
         <v>190</v>
       </c>
       <c r="G10" s="272"/>
       <c r="H10" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I10" s="307">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
       <c r="J10" s="119"/>
-      <c r="L10" s="450"/>
-      <c r="M10" s="450"/>
-      <c r="N10" s="450"/>
+      <c r="L10" s="448"/>
+      <c r="M10" s="448"/>
+      <c r="N10" s="448"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="352"/>
-      <c r="B11" s="452"/>
-      <c r="C11" s="462"/>
-      <c r="D11" s="464"/>
+      <c r="B11" s="450"/>
+      <c r="C11" s="454"/>
+      <c r="D11" s="456"/>
       <c r="E11" s="386" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F11" s="223">
         <v>210</v>
       </c>
       <c r="G11" s="272"/>
       <c r="H11" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I11" s="307">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
       <c r="J11" s="119"/>
-      <c r="L11" s="450"/>
-      <c r="M11" s="450"/>
-      <c r="N11" s="450"/>
+      <c r="L11" s="448"/>
+      <c r="M11" s="448"/>
+      <c r="N11" s="448"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="352"/>
-      <c r="B12" s="453"/>
+      <c r="B12" s="451"/>
       <c r="C12" s="222" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E12" s="386" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F12" s="223">
         <v>40</v>
       </c>
       <c r="G12" s="272"/>
       <c r="H12" s="222" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I12" s="307">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J12" s="119"/>
-      <c r="L12" s="450"/>
-      <c r="M12" s="450"/>
-      <c r="N12" s="450"/>
+      <c r="L12" s="448"/>
+      <c r="M12" s="448"/>
+      <c r="N12" s="448"/>
     </row>
     <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="352"/>
-      <c r="B13" s="451" t="s">
+      <c r="B13" s="449" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="452" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="460" t="s">
-        <v>105</v>
-      </c>
       <c r="D13" s="371" t="s">
+        <v>512</v>
+      </c>
+      <c r="E13" s="386" t="s">
         <v>513</v>
-      </c>
-      <c r="E13" s="386" t="s">
-        <v>514</v>
       </c>
       <c r="F13" s="223">
         <v>32</v>
       </c>
       <c r="G13" s="272"/>
       <c r="H13" s="222" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I13" s="307">
         <f>IF(ISBLANK(G13),F13,G13)</f>
         <v>32</v>
       </c>
       <c r="J13" s="119"/>
-      <c r="L13" s="450"/>
-      <c r="M13" s="450"/>
-      <c r="N13" s="450"/>
+      <c r="L13" s="448"/>
+      <c r="M13" s="448"/>
+      <c r="N13" s="448"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="352"/>
-      <c r="B14" s="452"/>
-      <c r="C14" s="461"/>
-      <c r="D14" s="465" t="s">
-        <v>515</v>
+      <c r="B14" s="450"/>
+      <c r="C14" s="453"/>
+      <c r="D14" s="463" t="s">
+        <v>514</v>
       </c>
       <c r="E14" s="386" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F14" s="223">
         <v>20</v>
       </c>
       <c r="G14" s="272"/>
       <c r="H14" s="222" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I14" s="307">
         <f>IF(ISBLANK(G14),F14,G14)</f>
         <v>20</v>
       </c>
       <c r="J14" s="119"/>
-      <c r="L14" s="450"/>
-      <c r="M14" s="450"/>
-      <c r="N14" s="450"/>
+      <c r="L14" s="448"/>
+      <c r="M14" s="448"/>
+      <c r="N14" s="448"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="352"/>
-      <c r="B15" s="452"/>
-      <c r="C15" s="461"/>
-      <c r="D15" s="463"/>
+      <c r="B15" s="450"/>
+      <c r="C15" s="453"/>
+      <c r="D15" s="455"/>
       <c r="E15" s="386" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F15" s="223">
         <v>28</v>
       </c>
       <c r="G15" s="272"/>
       <c r="H15" s="222" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I15" s="307">
         <f t="shared" ref="I15:I16" si="1">IF(ISBLANK(G15),F15,G15)</f>
         <v>28</v>
       </c>
       <c r="J15" s="119"/>
-      <c r="L15" s="450"/>
-      <c r="M15" s="450"/>
-      <c r="N15" s="450"/>
+      <c r="L15" s="448"/>
+      <c r="M15" s="448"/>
+      <c r="N15" s="448"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="352"/>
-      <c r="B16" s="452"/>
-      <c r="C16" s="462"/>
-      <c r="D16" s="464"/>
+      <c r="B16" s="450"/>
+      <c r="C16" s="454"/>
+      <c r="D16" s="456"/>
       <c r="E16" s="386" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F16" s="223">
         <v>32</v>
       </c>
       <c r="G16" s="272"/>
       <c r="H16" s="222" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I16" s="307">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="J16" s="119"/>
-      <c r="L16" s="450"/>
-      <c r="M16" s="450"/>
-      <c r="N16" s="450"/>
+      <c r="L16" s="448"/>
+      <c r="M16" s="448"/>
+      <c r="N16" s="448"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="437" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="452"/>
+      <c r="B17" s="450"/>
       <c r="C17" s="222" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E17" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G17" s="272"/>
       <c r="H17" s="222" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I17" s="307" t="str">
         <f>IF(ISBLANK(G17),"keine",G17)</f>
         <v>keine</v>
       </c>
       <c r="J17" s="119"/>
-      <c r="L17" s="450"/>
-      <c r="M17" s="450"/>
-      <c r="N17" s="450"/>
+      <c r="L17" s="448"/>
+      <c r="M17" s="448"/>
+      <c r="N17" s="448"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="437"/>
-      <c r="B18" s="452"/>
+      <c r="B18" s="450"/>
       <c r="C18" s="222" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D18" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E18" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F18" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G18" s="272"/>
       <c r="H18" s="222" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I18" s="307" t="str">
         <f>IF(ISBLANK(G18),"keine",G18)</f>
         <v>keine</v>
       </c>
       <c r="J18" s="119"/>
-      <c r="L18" s="450"/>
-      <c r="M18" s="450"/>
-      <c r="N18" s="450"/>
+      <c r="L18" s="448"/>
+      <c r="M18" s="448"/>
+      <c r="N18" s="448"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="437"/>
-      <c r="B19" s="453"/>
+      <c r="B19" s="451"/>
       <c r="C19" s="222" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D19" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E19" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F19" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G19" s="272"/>
       <c r="H19" s="222" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I19" s="307" t="str">
         <f>IF(ISBLANK(G19),"keine",G19)</f>
         <v>keine</v>
       </c>
       <c r="J19" s="119"/>
-      <c r="L19" s="450"/>
-      <c r="M19" s="450"/>
-      <c r="N19" s="450"/>
+      <c r="L19" s="448"/>
+      <c r="M19" s="448"/>
+      <c r="N19" s="448"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="352"/>
       <c r="B20" s="378"/>
       <c r="C20" s="380"/>
-      <c r="D20" s="466" t="s">
-        <v>519</v>
-      </c>
-      <c r="E20" s="467"/>
+      <c r="D20" s="464" t="s">
+        <v>518</v>
+      </c>
+      <c r="E20" s="465"/>
       <c r="F20" s="381"/>
       <c r="G20" s="382"/>
       <c r="H20" s="379"/>
       <c r="I20" s="307"/>
       <c r="J20" s="119"/>
-      <c r="L20" s="450"/>
-      <c r="M20" s="450"/>
-      <c r="N20" s="450"/>
+      <c r="L20" s="448"/>
+      <c r="M20" s="448"/>
+      <c r="N20" s="448"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="352"/>
-      <c r="B21" s="451" t="s">
+      <c r="B21" s="449" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="452" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="460" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="448" t="s">
-        <v>516</v>
-      </c>
-      <c r="E21" s="449"/>
+      <c r="D21" s="466" t="s">
+        <v>515</v>
+      </c>
+      <c r="E21" s="467"/>
       <c r="F21" s="386">
         <v>64</v>
       </c>
       <c r="G21" s="272"/>
       <c r="H21" s="222" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I21" s="307">
         <f>IF(ISBLANK(G21),F21,G21)</f>
         <v>64</v>
       </c>
       <c r="J21" s="119"/>
-      <c r="L21" s="450"/>
-      <c r="M21" s="450"/>
-      <c r="N21" s="450"/>
+      <c r="L21" s="448"/>
+      <c r="M21" s="448"/>
+      <c r="N21" s="448"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="352"/>
-      <c r="B22" s="452"/>
-      <c r="C22" s="461"/>
-      <c r="D22" s="448" t="s">
-        <v>517</v>
-      </c>
-      <c r="E22" s="449"/>
+      <c r="B22" s="450"/>
+      <c r="C22" s="453"/>
+      <c r="D22" s="466" t="s">
+        <v>516</v>
+      </c>
+      <c r="E22" s="467"/>
       <c r="F22" s="386">
         <v>84</v>
       </c>
       <c r="G22" s="272"/>
       <c r="H22" s="222" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I22" s="307">
         <f t="shared" ref="I22:I23" si="2">IF(ISBLANK(G22),F22,G22)</f>
@@ -22225,91 +22225,91 @@
       </c>
       <c r="J22" s="119"/>
       <c r="K22" s="383"/>
-      <c r="L22" s="450"/>
-      <c r="M22" s="450"/>
-      <c r="N22" s="450"/>
+      <c r="L22" s="448"/>
+      <c r="M22" s="448"/>
+      <c r="N22" s="448"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="352"/>
-      <c r="B23" s="453"/>
-      <c r="C23" s="462"/>
-      <c r="D23" s="448" t="s">
-        <v>518</v>
-      </c>
-      <c r="E23" s="449"/>
+      <c r="B23" s="451"/>
+      <c r="C23" s="454"/>
+      <c r="D23" s="466" t="s">
+        <v>517</v>
+      </c>
+      <c r="E23" s="467"/>
       <c r="F23" s="386">
         <v>100</v>
       </c>
       <c r="G23" s="272"/>
       <c r="H23" s="222" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" s="307">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="J23" s="119"/>
-      <c r="L23" s="450"/>
-      <c r="M23" s="450"/>
-      <c r="N23" s="450"/>
+      <c r="L23" s="448"/>
+      <c r="M23" s="448"/>
+      <c r="N23" s="448"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="352"/>
       <c r="B24" s="367" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="369" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="448" t="s">
-        <v>520</v>
-      </c>
-      <c r="E24" s="449"/>
+        <v>101</v>
+      </c>
+      <c r="D24" s="466" t="s">
+        <v>519</v>
+      </c>
+      <c r="E24" s="467"/>
       <c r="F24" s="388">
         <v>3.6</v>
       </c>
       <c r="G24" s="272"/>
       <c r="H24" s="222" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I24" s="307">
         <f>IF(ISBLANK(G24),F24,G24)</f>
         <v>3.6</v>
       </c>
       <c r="J24" s="119"/>
-      <c r="L24" s="450"/>
-      <c r="M24" s="450"/>
-      <c r="N24" s="450"/>
+      <c r="L24" s="448"/>
+      <c r="M24" s="448"/>
+      <c r="N24" s="448"/>
     </row>
     <row r="25" spans="1:14" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25" s="353"/>
       <c r="B25" s="356" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C25" s="225" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E25" s="223" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F25" s="224">
         <v>60</v>
       </c>
       <c r="G25" s="273"/>
       <c r="H25" s="225" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I25" s="307">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J25" s="191"/>
-      <c r="L25" s="450"/>
-      <c r="M25" s="450"/>
-      <c r="N25" s="450"/>
+      <c r="L25" s="448"/>
+      <c r="M25" s="448"/>
+      <c r="N25" s="448"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="119"/>
@@ -22338,13 +22338,13 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="193"/>
       <c r="B29" s="192" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="192"/>
       <c r="D29" s="192"/>
       <c r="E29" s="192"/>
       <c r="F29" s="193" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G29" s="193"/>
       <c r="H29" s="193"/>
@@ -22368,7 +22368,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="196"/>
       <c r="B31" s="293" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C31" s="339"/>
       <c r="D31" s="339"/>
@@ -22396,17 +22396,17 @@
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="196"/>
       <c r="B33" s="346" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="327"/>
       <c r="D33" s="327"/>
       <c r="E33" s="327"/>
       <c r="F33" s="296" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G33" s="347"/>
       <c r="H33" s="295" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I33" s="194"/>
       <c r="J33" s="195"/>
@@ -22420,23 +22420,23 @@
       <c r="E34" s="327"/>
       <c r="F34" s="209"/>
       <c r="G34" s="210" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H34" s="294"/>
       <c r="I34" s="308" t="s">
+        <v>110</v>
+      </c>
+      <c r="J34" s="198" t="s">
         <v>111</v>
       </c>
-      <c r="J34" s="198" t="s">
+      <c r="K34" s="255" t="s">
         <v>112</v>
-      </c>
-      <c r="K34" s="255" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="204"/>
       <c r="B35" s="212" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C35" s="372"/>
       <c r="D35" s="375"/>
@@ -22446,21 +22446,21 @@
       </c>
       <c r="G35" s="243"/>
       <c r="H35" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I35" s="308">
         <f>IF(ISNUMBER(G35),G35,F35)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="J35" s="199" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K35" s="254"/>
     </row>
     <row r="36" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="204"/>
       <c r="B36" s="215" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C36" s="373"/>
       <c r="D36" s="376"/>
@@ -22470,21 +22470,21 @@
       </c>
       <c r="G36" s="243"/>
       <c r="H36" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I36" s="308">
         <f>IF(ISNUMBER(G36),G36,F36)/100</f>
         <v>0.59</v>
       </c>
       <c r="J36" s="199" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K36" s="254"/>
     </row>
     <row r="37" spans="1:11" ht="14.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="205"/>
       <c r="B37" s="216" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="374"/>
       <c r="D37" s="377"/>
@@ -22500,9 +22500,9 @@
       <c r="K37" s="254"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="456"/>
+      <c r="A38" s="459"/>
       <c r="B38" s="212" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="372"/>
       <c r="D38" s="375"/>
@@ -22512,21 +22512,21 @@
       </c>
       <c r="G38" s="243"/>
       <c r="H38" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I38" s="308">
         <f t="shared" ref="I38:I40" si="3">IF(ISNUMBER(G38),G38,F38)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="J38" s="199" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K38" s="254"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="456"/>
+      <c r="A39" s="459"/>
       <c r="B39" s="212" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="372"/>
       <c r="D39" s="375"/>
@@ -22536,21 +22536,21 @@
       </c>
       <c r="G39" s="243"/>
       <c r="H39" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I39" s="308">
         <f t="shared" si="3"/>
         <v>1.788</v>
       </c>
       <c r="J39" s="199" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K39" s="254"/>
     </row>
     <row r="40" spans="1:11" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A40" s="205"/>
       <c r="B40" s="212" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" s="372"/>
       <c r="D40" s="375"/>
@@ -22560,14 +22560,14 @@
       </c>
       <c r="G40" s="243"/>
       <c r="H40" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I40" s="308">
         <f t="shared" si="3"/>
         <v>1.3</v>
       </c>
       <c r="J40" s="199" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K40" s="254"/>
     </row>
@@ -22600,7 +22600,7 @@
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="193"/>
       <c r="B43" s="293" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C43" s="339"/>
       <c r="D43" s="339"/>
@@ -22614,17 +22614,17 @@
     </row>
     <row r="44" spans="1:11" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="457" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" s="458"/>
-      <c r="D44" s="458"/>
-      <c r="E44" s="458"/>
-      <c r="F44" s="458"/>
-      <c r="G44" s="458"/>
-      <c r="H44" s="459"/>
+      <c r="B44" s="460" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="461"/>
+      <c r="D44" s="461"/>
+      <c r="E44" s="461"/>
+      <c r="F44" s="461"/>
+      <c r="G44" s="461"/>
+      <c r="H44" s="462"/>
       <c r="I44" s="308" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J44" s="202"/>
       <c r="K44" s="202"/>
@@ -22637,10 +22637,10 @@
       <c r="E45" s="327"/>
       <c r="F45" s="327"/>
       <c r="G45" s="342" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" s="343" t="s">
         <v>96</v>
-      </c>
-      <c r="H45" s="343" t="s">
-        <v>97</v>
       </c>
       <c r="I45" s="308"/>
       <c r="J45" s="195"/>
@@ -22649,7 +22649,7 @@
     <row r="46" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A46" s="207"/>
       <c r="B46" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C46" s="327"/>
       <c r="D46" s="327"/>
@@ -22667,7 +22667,7 @@
         <v>860</v>
       </c>
       <c r="J46" s="199" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K46" s="254"/>
     </row>
@@ -22687,7 +22687,7 @@
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="193"/>
       <c r="B48" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" s="327"/>
       <c r="D48" s="327"/>
@@ -22697,21 +22697,21 @@
       </c>
       <c r="G48" s="243"/>
       <c r="H48" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I48" s="308">
         <f>IF(ISNUMBER(G48),G48,F48)</f>
         <v>0.02</v>
       </c>
       <c r="J48" s="199" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K48" s="254"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="193"/>
       <c r="B49" s="215" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C49" s="72"/>
       <c r="D49" s="72"/>
@@ -22721,14 +22721,14 @@
       </c>
       <c r="G49" s="243"/>
       <c r="H49" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I49" s="308">
         <f>IF(ISNUMBER(G49),G49,F49)</f>
         <v>0.15</v>
       </c>
       <c r="J49" s="199" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K49" s="254"/>
     </row>
@@ -22761,7 +22761,7 @@
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="193"/>
       <c r="B52" s="293" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C52" s="340"/>
       <c r="D52" s="340"/>
@@ -22775,10 +22775,10 @@
     </row>
     <row r="53" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="193"/>
-      <c r="B53" s="454" t="s">
-        <v>401</v>
-      </c>
-      <c r="C53" s="455"/>
+      <c r="B53" s="457" t="s">
+        <v>400</v>
+      </c>
+      <c r="C53" s="458"/>
       <c r="D53" s="368"/>
       <c r="E53" s="368"/>
       <c r="F53" s="218">
@@ -22786,21 +22786,21 @@
       </c>
       <c r="G53" s="243"/>
       <c r="H53" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I53" s="308">
         <f>IF(ISNUMBER(G53),G53,F53)</f>
         <v>84</v>
       </c>
       <c r="J53" s="199" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K53" s="254"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="193"/>
       <c r="B54" s="246" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" s="247"/>
       <c r="D54" s="247"/>
@@ -22849,52 +22849,52 @@
     <mergeCell ref="D8:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="K35">
-    <cfRule type="expression" dxfId="73" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>G35&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36">
-    <cfRule type="expression" dxfId="72" priority="9">
+    <cfRule type="expression" dxfId="13" priority="9">
       <formula>G36&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="expression" dxfId="71" priority="8">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>G38&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="expression" dxfId="70" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>G39&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="expression" dxfId="69" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>G40&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K46">
-    <cfRule type="expression" dxfId="68" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>G46&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48">
-    <cfRule type="expression" dxfId="67" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>G48&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="expression" dxfId="66" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>G49&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53">
-    <cfRule type="expression" dxfId="65" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>G53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>SUM(G35:G53)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22930,7 +22930,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -22943,7 +22943,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
@@ -22957,7 +22957,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="54">
         <v>1</v>
@@ -22969,7 +22969,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter1=0,"",Anbieter1)</f>
@@ -22989,14 +22989,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="102"/>
       <c r="F9" s="125"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller1=0,"",Hersteller1)</f>
@@ -23007,7 +23007,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell1=0,"",Modell1)</f>
@@ -23018,7 +23018,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo1=0,"",Zusatzinfo1)</f>
@@ -23029,7 +23029,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart1=0,"",Antriebsart1)</f>
@@ -23040,7 +23040,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="107"/>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie1=0,"",Energie1)</f>
@@ -23057,7 +23057,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23071,7 +23071,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
@@ -23082,33 +23082,33 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
@@ -23122,14 +23122,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="125"/>
     </row>
@@ -23141,7 +23141,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23" s="125"/>
     </row>
@@ -23152,7 +23152,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="89"/>
       <c r="D25" s="89"/>
@@ -23163,7 +23163,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23171,39 +23171,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,8,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -23212,7 +23212,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1)</f>
@@ -23223,63 +23223,63 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F33" s="107"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="279">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="279">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -23287,7 +23287,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1,IF(Antriebsart1="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23297,32 +23297,32 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="107"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" s="89"/>
       <c r="D43" s="89"/>
@@ -23336,10 +23336,10 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="62"/>
     </row>
@@ -23348,14 +23348,14 @@
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="107"/>
@@ -23368,21 +23368,21 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="107"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,19 +23401,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B54" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F54" s="58"/>
     </row>
@@ -23422,66 +23422,66 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F55" s="58"/>
     </row>
     <row r="56" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="58"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="330" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
@@ -23537,14 +23537,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F63" s="58"/>
     </row>
@@ -23553,26 +23553,26 @@
     </row>
     <row r="65" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -23585,7 +23585,7 @@
     <mergeCell ref="A60:A62"/>
   </mergeCells>
   <conditionalFormatting sqref="A16:D23">
-    <cfRule type="expression" dxfId="63" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>Antriebsart1&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23622,7 +23622,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23635,7 +23635,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -23651,7 +23651,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="54">
         <v>2</v>
@@ -23664,7 +23664,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter2=0,"",Anbieter2)</f>
@@ -23686,7 +23686,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -23694,7 +23694,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller2=0,"",Hersteller2)</f>
@@ -23706,7 +23706,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell2=0,"",Modell2)</f>
@@ -23718,7 +23718,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo2=0,"",Zusatzinfo2)</f>
@@ -23730,7 +23730,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart2=0,"",Antriebsart2)</f>
@@ -23741,7 +23741,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie2=0,"",Energie2)</f>
@@ -23757,7 +23757,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23773,7 +23773,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
@@ -23785,35 +23785,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
@@ -23828,14 +23828,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -23860,7 +23860,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -23873,7 +23873,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23882,42 +23882,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,8,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -23930,7 +23930,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2)</f>
@@ -23942,70 +23942,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -24018,7 +24018,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2,IF(Antriebsart2="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -24030,28 +24030,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -24062,7 +24062,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -24079,10 +24079,10 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
@@ -24093,14 +24093,14 @@
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
@@ -24113,21 +24113,21 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -24151,20 +24151,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -24174,67 +24174,67 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="330" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
@@ -24290,14 +24290,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -24312,26 +24312,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -24345,7 +24345,7 @@
     <mergeCell ref="A60:A62"/>
   </mergeCells>
   <conditionalFormatting sqref="A16:D23">
-    <cfRule type="expression" dxfId="62" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>Antriebsart2&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24382,7 +24382,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24395,7 +24395,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -24411,7 +24411,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="54">
         <v>3</v>
@@ -24424,7 +24424,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter3=0,"",Anbieter3)</f>
@@ -24446,7 +24446,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -24454,7 +24454,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller3=0,"",Hersteller3)</f>
@@ -24466,7 +24466,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell3=0,"",Modell3)</f>
@@ -24478,7 +24478,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo3=0,"",Zusatzinfo3)</f>
@@ -24490,7 +24490,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart3=0,"",Antriebsart3)</f>
@@ -24501,7 +24501,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie3=0,"",Energie3)</f>
@@ -24517,7 +24517,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -24533,7 +24533,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
@@ -24545,35 +24545,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
@@ -24588,14 +24588,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -24608,7 +24608,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -24620,7 +24620,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -24633,7 +24633,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -24642,42 +24642,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,8,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -24690,7 +24690,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3)</f>
@@ -24702,70 +24702,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -24778,7 +24778,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3,IF(Antriebsart3="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -24790,28 +24790,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -24822,7 +24822,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -24839,10 +24839,10 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
@@ -24853,14 +24853,14 @@
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="133"/>
@@ -24873,21 +24873,21 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="133"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C48" s="279" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -24911,20 +24911,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -24934,67 +24934,67 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="327" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="328" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="327" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
@@ -25050,14 +25050,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="284" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -25072,26 +25072,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" s="285" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -25105,7 +25105,7 @@
     <mergeCell ref="A60:A62"/>
   </mergeCells>
   <conditionalFormatting sqref="A16:D23">
-    <cfRule type="expression" dxfId="61" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>Antriebsart3&lt;&gt;"Plug-In-Hybrid (PHEV)"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25120,17 +25120,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -25139,7 +25128,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -25368,24 +25357,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -25393,7 +25376,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25410,4 +25393,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\Online-Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/B2 - LZK-Rechner LNF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57FFC95-8146-4260-848E-B11F6662749F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{91E35081-D1C7-4439-AB28-1F61A1A8072A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D9A87CE8-C110-4C1E-AC21-1873A7D644F5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2602,49 +2602,6 @@
     <t>Gesellschaftliche Kosten von Umweltbelastungen - Klimakosten von Treibhausgas-Emissionen (02.07.2024)</t>
   </si>
   <si>
-    <r>
-      <t>Der Excel-Rechner ist</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ohne Passwort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können.</t>
-    </r>
-  </si>
-  <si>
     <t>Angaben zu den Energiekosten</t>
   </si>
   <si>
@@ -3456,6 +3413,49 @@
   </si>
   <si>
     <t>Ladeverhalten Elektrofahrzeug</t>
+  </si>
+  <si>
+    <r>
+      <t>Der Excel-Rechner ist</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ohne Passwort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5770,6 +5770,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -5804,15 +5813,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -5958,65 +5958,65 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -14294,7 +14294,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -14304,7 +14304,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14326,17 +14326,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="391" t="s">
-        <v>521</v>
-      </c>
-      <c r="C5" s="391"/>
-      <c r="D5" s="391"/>
-      <c r="E5" s="391"/>
-      <c r="F5" s="391"/>
-      <c r="G5" s="391"/>
-      <c r="H5" s="391"/>
-      <c r="I5" s="391"/>
-      <c r="J5" s="391"/>
+      <c r="B5" s="394" t="s">
+        <v>520</v>
+      </c>
+      <c r="C5" s="394"/>
+      <c r="D5" s="394"/>
+      <c r="E5" s="394"/>
+      <c r="F5" s="394"/>
+      <c r="G5" s="394"/>
+      <c r="H5" s="394"/>
+      <c r="I5" s="394"/>
+      <c r="J5" s="394"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14374,13 +14374,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="392" t="s">
-        <v>403</v>
-      </c>
-      <c r="G9" s="392"/>
-      <c r="H9" s="392"/>
-      <c r="I9" s="392"/>
-      <c r="J9" s="392"/>
+      <c r="F9" s="395" t="s">
+        <v>402</v>
+      </c>
+      <c r="G9" s="395"/>
+      <c r="H9" s="395"/>
+      <c r="I9" s="395"/>
+      <c r="J9" s="395"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14394,31 +14394,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="393" t="s">
-        <v>418</v>
-      </c>
-      <c r="G11" s="394"/>
-      <c r="H11" s="394"/>
-      <c r="I11" s="394"/>
-      <c r="J11" s="394"/>
+      <c r="F11" s="396" t="s">
+        <v>417</v>
+      </c>
+      <c r="G11" s="397"/>
+      <c r="H11" s="397"/>
+      <c r="I11" s="397"/>
+      <c r="J11" s="397"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="394"/>
-      <c r="G12" s="394"/>
-      <c r="H12" s="394"/>
-      <c r="I12" s="394"/>
-      <c r="J12" s="394"/>
+      <c r="F12" s="397"/>
+      <c r="G12" s="397"/>
+      <c r="H12" s="397"/>
+      <c r="I12" s="397"/>
+      <c r="J12" s="397"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="394"/>
-      <c r="G13" s="394"/>
-      <c r="H13" s="394"/>
-      <c r="I13" s="394"/>
-      <c r="J13" s="394"/>
+      <c r="F13" s="397"/>
+      <c r="G13" s="397"/>
+      <c r="H13" s="397"/>
+      <c r="I13" s="397"/>
+      <c r="J13" s="397"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14432,22 +14432,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="395" t="s">
+      <c r="F15" s="398" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="396"/>
-      <c r="H15" s="396"/>
-      <c r="I15" s="396"/>
-      <c r="J15" s="396"/>
+      <c r="G15" s="399"/>
+      <c r="H15" s="399"/>
+      <c r="I15" s="399"/>
+      <c r="J15" s="399"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="396"/>
-      <c r="G16" s="396"/>
-      <c r="H16" s="396"/>
-      <c r="I16" s="396"/>
-      <c r="J16" s="396"/>
+      <c r="F16" s="399"/>
+      <c r="G16" s="399"/>
+      <c r="H16" s="399"/>
+      <c r="I16" s="399"/>
+      <c r="J16" s="399"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14461,13 +14461,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="397" t="s">
+      <c r="F18" s="400" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="398"/>
-      <c r="H18" s="398"/>
-      <c r="I18" s="398"/>
-      <c r="J18" s="398"/>
+      <c r="G18" s="401"/>
+      <c r="H18" s="401"/>
+      <c r="I18" s="401"/>
+      <c r="J18" s="401"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14481,31 +14481,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="399" t="s">
+      <c r="F20" s="402" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="399"/>
-      <c r="H20" s="399"/>
-      <c r="I20" s="399"/>
-      <c r="J20" s="399"/>
+      <c r="G20" s="402"/>
+      <c r="H20" s="402"/>
+      <c r="I20" s="402"/>
+      <c r="J20" s="402"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="399"/>
-      <c r="G21" s="399"/>
-      <c r="H21" s="399"/>
-      <c r="I21" s="399"/>
-      <c r="J21" s="399"/>
+      <c r="F21" s="402"/>
+      <c r="G21" s="402"/>
+      <c r="H21" s="402"/>
+      <c r="I21" s="402"/>
+      <c r="J21" s="402"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="399"/>
-      <c r="G22" s="399"/>
-      <c r="H22" s="399"/>
-      <c r="I22" s="399"/>
-      <c r="J22" s="399"/>
+      <c r="F22" s="402"/>
+      <c r="G22" s="402"/>
+      <c r="H22" s="402"/>
+      <c r="I22" s="402"/>
+      <c r="J22" s="402"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14519,22 +14519,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="400" t="s">
+      <c r="F24" s="403" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="400"/>
-      <c r="H24" s="400"/>
-      <c r="I24" s="400"/>
-      <c r="J24" s="400"/>
+      <c r="G24" s="403"/>
+      <c r="H24" s="403"/>
+      <c r="I24" s="403"/>
+      <c r="J24" s="403"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="400"/>
-      <c r="G25" s="400"/>
-      <c r="H25" s="400"/>
-      <c r="I25" s="400"/>
-      <c r="J25" s="400"/>
+      <c r="F25" s="403"/>
+      <c r="G25" s="403"/>
+      <c r="H25" s="403"/>
+      <c r="I25" s="403"/>
+      <c r="J25" s="403"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14548,49 +14548,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="390"/>
-      <c r="G27" s="390"/>
-      <c r="H27" s="390"/>
-      <c r="I27" s="390"/>
-      <c r="J27" s="390"/>
+      <c r="F27" s="393"/>
+      <c r="G27" s="393"/>
+      <c r="H27" s="393"/>
+      <c r="I27" s="393"/>
+      <c r="J27" s="393"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="401" t="s">
-        <v>419</v>
-      </c>
-      <c r="G28" s="401"/>
-      <c r="H28" s="401"/>
-      <c r="I28" s="401"/>
-      <c r="J28" s="401"/>
+      <c r="F28" s="404" t="s">
+        <v>418</v>
+      </c>
+      <c r="G28" s="404"/>
+      <c r="H28" s="404"/>
+      <c r="I28" s="404"/>
+      <c r="J28" s="404"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="401"/>
-      <c r="G29" s="401"/>
-      <c r="H29" s="401"/>
-      <c r="I29" s="401"/>
-      <c r="J29" s="401"/>
+      <c r="F29" s="404"/>
+      <c r="G29" s="404"/>
+      <c r="H29" s="404"/>
+      <c r="I29" s="404"/>
+      <c r="J29" s="404"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="401"/>
-      <c r="G30" s="401"/>
-      <c r="H30" s="401"/>
-      <c r="I30" s="401"/>
-      <c r="J30" s="401"/>
+      <c r="F30" s="404"/>
+      <c r="G30" s="404"/>
+      <c r="H30" s="404"/>
+      <c r="I30" s="404"/>
+      <c r="J30" s="404"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="402"/>
-      <c r="G31" s="402"/>
-      <c r="H31" s="402"/>
-      <c r="I31" s="402"/>
-      <c r="J31" s="402"/>
+      <c r="F31" s="392"/>
+      <c r="G31" s="392"/>
+      <c r="H31" s="392"/>
+      <c r="I31" s="392"/>
+      <c r="J31" s="392"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14639,15 +14639,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="402" t="s">
+      <c r="D36" s="392" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="402"/>
-      <c r="F36" s="402"/>
-      <c r="G36" s="402"/>
-      <c r="H36" s="402"/>
-      <c r="I36" s="402"/>
-      <c r="J36" s="402"/>
+      <c r="E36" s="392"/>
+      <c r="F36" s="392"/>
+      <c r="G36" s="392"/>
+      <c r="H36" s="392"/>
+      <c r="I36" s="392"/>
+      <c r="J36" s="392"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14663,24 +14663,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="390" t="s">
+      <c r="D38" s="393" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="390"/>
-      <c r="F38" s="390"/>
-      <c r="G38" s="390"/>
-      <c r="H38" s="390"/>
-      <c r="I38" s="390"/>
-      <c r="J38" s="390"/>
+      <c r="E38" s="393"/>
+      <c r="F38" s="393"/>
+      <c r="G38" s="393"/>
+      <c r="H38" s="393"/>
+      <c r="I38" s="393"/>
+      <c r="J38" s="393"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="390"/>
-      <c r="E39" s="390"/>
-      <c r="F39" s="390"/>
-      <c r="G39" s="390"/>
-      <c r="H39" s="390"/>
-      <c r="I39" s="390"/>
-      <c r="J39" s="390"/>
+      <c r="D39" s="393"/>
+      <c r="E39" s="393"/>
+      <c r="F39" s="393"/>
+      <c r="G39" s="393"/>
+      <c r="H39" s="393"/>
+      <c r="I39" s="393"/>
+      <c r="J39" s="393"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14698,15 +14698,15 @@
         <v>9</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="403" t="s">
+      <c r="D41" s="390" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="403"/>
-      <c r="F41" s="403"/>
-      <c r="G41" s="403"/>
-      <c r="H41" s="403"/>
-      <c r="I41" s="403"/>
-      <c r="J41" s="403"/>
+      <c r="E41" s="390"/>
+      <c r="F41" s="390"/>
+      <c r="G41" s="390"/>
+      <c r="H41" s="390"/>
+      <c r="I41" s="390"/>
+      <c r="J41" s="390"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14720,30 +14720,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="404" t="s">
+      <c r="B43" s="391" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="402" t="s">
+      <c r="D43" s="392" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="402"/>
-      <c r="F43" s="402"/>
-      <c r="G43" s="402"/>
-      <c r="H43" s="402"/>
-      <c r="I43" s="402"/>
-      <c r="J43" s="402"/>
+      <c r="E43" s="392"/>
+      <c r="F43" s="392"/>
+      <c r="G43" s="392"/>
+      <c r="H43" s="392"/>
+      <c r="I43" s="392"/>
+      <c r="J43" s="392"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="404"/>
+      <c r="B44" s="391"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="402"/>
-      <c r="E44" s="402"/>
-      <c r="F44" s="402"/>
-      <c r="G44" s="402"/>
-      <c r="H44" s="402"/>
-      <c r="I44" s="402"/>
-      <c r="J44" s="402"/>
+      <c r="D44" s="392"/>
+      <c r="E44" s="392"/>
+      <c r="F44" s="392"/>
+      <c r="G44" s="392"/>
+      <c r="H44" s="392"/>
+      <c r="I44" s="392"/>
+      <c r="J44" s="392"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14754,18 +14754,18 @@
       <c r="I45" s="114"/>
       <c r="J45" s="114"/>
     </row>
-    <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="402" t="s">
-        <v>394</v>
-      </c>
-      <c r="C46" s="402"/>
-      <c r="D46" s="402"/>
-      <c r="E46" s="402"/>
-      <c r="F46" s="402"/>
-      <c r="G46" s="402"/>
-      <c r="H46" s="402"/>
-      <c r="I46" s="402"/>
-      <c r="J46" s="402"/>
+    <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="392" t="s">
+        <v>609</v>
+      </c>
+      <c r="C46" s="392"/>
+      <c r="D46" s="392"/>
+      <c r="E46" s="392"/>
+      <c r="F46" s="392"/>
+      <c r="G46" s="392"/>
+      <c r="H46" s="392"/>
+      <c r="I46" s="392"/>
+      <c r="J46" s="392"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14800,17 +14800,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="402" t="s">
+      <c r="B50" s="392" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="402"/>
-      <c r="D50" s="402"/>
-      <c r="E50" s="402"/>
-      <c r="F50" s="402"/>
-      <c r="G50" s="402"/>
-      <c r="H50" s="402"/>
-      <c r="I50" s="402"/>
-      <c r="J50" s="402"/>
+      <c r="C50" s="392"/>
+      <c r="D50" s="392"/>
+      <c r="E50" s="392"/>
+      <c r="F50" s="392"/>
+      <c r="G50" s="392"/>
+      <c r="H50" s="392"/>
+      <c r="I50" s="392"/>
+      <c r="J50" s="392"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14873,11 +14873,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14890,6 +14885,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15398,7 +15398,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
@@ -15415,7 +15415,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
+      <c r="A47" s="391"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -15483,7 +15483,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -15548,7 +15548,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15566,7 +15566,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
+      <c r="A61" s="391"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15582,7 +15582,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
+      <c r="A62" s="391"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15691,7 +15691,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -16162,7 +16162,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
@@ -16179,7 +16179,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
+      <c r="A47" s="391"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -16247,7 +16247,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -16312,7 +16312,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -16330,7 +16330,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
+      <c r="A61" s="391"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16346,7 +16346,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
+      <c r="A62" s="391"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -16458,7 +16458,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16520,7 +16520,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16622,14 +16622,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16645,13 +16645,13 @@
         <v>111</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16793,7 +16793,7 @@
         <v>172</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16972,12 +16972,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16993,12 +16993,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -17013,10 +17013,10 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -17024,7 +17024,7 @@
         <v>192</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -17032,7 +17032,7 @@
         <v>193</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -17040,7 +17040,7 @@
         <v>194</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -17048,7 +17048,7 @@
         <v>28</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -17056,7 +17056,7 @@
         <v>195</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -17064,23 +17064,23 @@
         <v>196</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -17088,15 +17088,15 @@
         <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17104,7 +17104,7 @@
         <v>198</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
@@ -17192,7 +17192,7 @@
         <v>219</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
@@ -17200,7 +17200,7 @@
         <v>221</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
@@ -17208,7 +17208,7 @@
         <v>223</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
@@ -17216,7 +17216,7 @@
         <v>225</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
@@ -17224,7 +17224,7 @@
         <v>227</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
@@ -17309,7 +17309,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>250</v>
@@ -17317,7 +17317,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>252</v>
@@ -17325,7 +17325,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>254</v>
@@ -17333,7 +17333,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>256</v>
@@ -17341,7 +17341,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>258</v>
@@ -17709,146 +17709,146 @@
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17896,7 +17896,7 @@
         <v>366</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
@@ -17904,7 +17904,7 @@
         <v>349</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17912,7 +17912,7 @@
         <v>350</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
@@ -17920,7 +17920,7 @@
         <v>351</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
@@ -17928,71 +17928,71 @@
         <v>352</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -18000,63 +18000,63 @@
         <v>353</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -18064,7 +18064,7 @@
         <v>354</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -18072,7 +18072,7 @@
         <v>355</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -18080,7 +18080,7 @@
         <v>181</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -18088,7 +18088,7 @@
         <v>356</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -18096,7 +18096,7 @@
         <v>361</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -18104,7 +18104,7 @@
         <v>182</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -18112,7 +18112,7 @@
         <v>357</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -18120,7 +18120,7 @@
         <v>362</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -18128,7 +18128,7 @@
         <v>183</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
@@ -18136,7 +18136,7 @@
         <v>358</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -18144,7 +18144,7 @@
         <v>363</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
@@ -18152,7 +18152,7 @@
         <v>185</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
@@ -18160,7 +18160,7 @@
         <v>359</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
@@ -18168,7 +18168,7 @@
         <v>364</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
@@ -18176,7 +18176,7 @@
         <v>186</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
@@ -18184,7 +18184,7 @@
         <v>360</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
@@ -18192,7 +18192,7 @@
         <v>365</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
@@ -18200,7 +18200,7 @@
         <v>367</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
@@ -18208,7 +18208,7 @@
         <v>368</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
@@ -18216,7 +18216,7 @@
         <v>369</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
@@ -18224,7 +18224,7 @@
         <v>370</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
@@ -18240,7 +18240,7 @@
         <v>373</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
@@ -18248,31 +18248,31 @@
         <v>374</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -18404,7 +18404,7 @@
         <v>182</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18468,7 +18468,7 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18477,17 +18477,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="5"/>
@@ -18496,32 +18496,32 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -18530,17 +18530,17 @@
     </row>
     <row r="41" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B41" s="385" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B42" s="385" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B43" s="385" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -18594,7 +18594,7 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C4" s="275" t="s">
         <v>376</v>
@@ -18607,23 +18607,23 @@
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>436</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18660,15 +18660,15 @@
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18686,15 +18686,15 @@
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18712,20 +18712,20 @@
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>415</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>416</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C24" s="275" t="s">
         <v>393</v>
@@ -18738,15 +18738,15 @@
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18795,7 +18795,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>20</v>
@@ -18814,7 +18814,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C6" s="409"/>
       <c r="D6" s="410"/>
@@ -18881,11 +18881,11 @@
       <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="404" t="s">
+      <c r="A13" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C13" s="406"/>
       <c r="D13" s="407"/>
@@ -18895,9 +18895,9 @@
       <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="404"/>
+      <c r="A14" s="391"/>
       <c r="B14" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C14" s="406"/>
       <c r="D14" s="407"/>
@@ -18916,7 +18916,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C16" s="152"/>
       <c r="D16" s="55" t="s">
@@ -18956,7 +18956,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B20" s="298" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C20" s="151"/>
       <c r="D20" s="55"/>
@@ -19015,7 +19015,7 @@
         <v>33</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F27" s="274">
         <f>Grunddaten!G46</f>
@@ -19027,7 +19027,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" s="154" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -19236,7 +19236,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -19387,7 +19387,7 @@
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="432" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M10" s="432"/>
       <c r="N10" s="236"/>
@@ -19442,7 +19442,7 @@
     </row>
     <row r="13" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="165" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D13" s="384"/>
       <c r="E13" s="139"/>
@@ -19705,7 +19705,7 @@
     </row>
     <row r="24" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C24" s="77" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D24" s="228"/>
       <c r="E24" s="389"/>
@@ -19720,7 +19720,7 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="404" t="s">
+      <c r="B25" s="391" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="331"/>
@@ -19739,7 +19739,7 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="404"/>
+      <c r="B26" s="391"/>
       <c r="C26" s="331"/>
       <c r="D26" s="322" t="s">
         <v>142</v>
@@ -19756,7 +19756,7 @@
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="404"/>
+      <c r="B27" s="391"/>
       <c r="C27" s="335"/>
       <c r="D27" s="322" t="s">
         <v>142</v>
@@ -19832,7 +19832,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -20225,7 +20225,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20239,7 +20239,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20282,7 +20282,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20364,7 +20364,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20859,7 +20859,7 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C31" s="317" t="s">
         <v>87</v>
@@ -20889,10 +20889,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D32" s="312" t="e">
         <f>SUM(D30:D31)</f>
@@ -21049,7 +21049,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -21063,7 +21063,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -21106,7 +21106,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -21188,7 +21188,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21228,7 +21228,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21525,7 +21525,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>87</v>
@@ -21555,10 +21555,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D27" s="312" t="e">
         <f>SUM(D25:D26)</f>
@@ -21584,7 +21584,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21752,7 +21752,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21764,7 +21764,7 @@
       <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="404" t="s">
+      <c r="A5" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="219"/>
@@ -21776,14 +21776,14 @@
       <c r="H5" s="219"/>
       <c r="I5" s="190"/>
       <c r="J5" s="119"/>
-      <c r="L5" s="448" t="s">
-        <v>399</v>
-      </c>
-      <c r="M5" s="448"/>
-      <c r="N5" s="448"/>
+      <c r="L5" s="467" t="s">
+        <v>398</v>
+      </c>
+      <c r="M5" s="467"/>
+      <c r="N5" s="467"/>
     </row>
     <row r="6" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="404"/>
+      <c r="A6" s="391"/>
       <c r="B6" s="220" t="s">
         <v>93</v>
       </c>
@@ -21791,10 +21791,10 @@
         <v>42</v>
       </c>
       <c r="D6" s="221" t="s">
+        <v>509</v>
+      </c>
+      <c r="E6" s="221" t="s">
         <v>510</v>
-      </c>
-      <c r="E6" s="221" t="s">
-        <v>511</v>
       </c>
       <c r="F6" s="221" t="s">
         <v>94</v>
@@ -21809,23 +21809,23 @@
         <v>97</v>
       </c>
       <c r="J6" s="119"/>
-      <c r="L6" s="448"/>
-      <c r="M6" s="448"/>
-      <c r="N6" s="448"/>
+      <c r="L6" s="467"/>
+      <c r="M6" s="467"/>
+      <c r="N6" s="467"/>
     </row>
     <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="352"/>
-      <c r="B7" s="449" t="s">
+      <c r="B7" s="454" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="452" t="s">
+      <c r="C7" s="460" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="370" t="s">
+        <v>511</v>
+      </c>
+      <c r="E7" s="386" t="s">
         <v>512</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>513</v>
       </c>
       <c r="F7" s="223">
         <v>230</v>
@@ -21839,19 +21839,19 @@
         <v>230</v>
       </c>
       <c r="J7" s="119"/>
-      <c r="L7" s="448"/>
-      <c r="M7" s="448"/>
-      <c r="N7" s="448"/>
+      <c r="L7" s="467"/>
+      <c r="M7" s="467"/>
+      <c r="N7" s="467"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="352"/>
-      <c r="B8" s="450"/>
-      <c r="C8" s="453"/>
-      <c r="D8" s="455" t="s">
-        <v>514</v>
+      <c r="B8" s="455"/>
+      <c r="C8" s="461"/>
+      <c r="D8" s="458" t="s">
+        <v>513</v>
       </c>
       <c r="E8" s="387" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F8" s="223">
         <v>150</v>
@@ -21865,17 +21865,17 @@
         <v>150</v>
       </c>
       <c r="J8" s="119"/>
-      <c r="L8" s="448"/>
-      <c r="M8" s="448"/>
-      <c r="N8" s="448"/>
+      <c r="L8" s="467"/>
+      <c r="M8" s="467"/>
+      <c r="N8" s="467"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="352"/>
-      <c r="B9" s="450"/>
-      <c r="C9" s="453"/>
-      <c r="D9" s="455"/>
+      <c r="B9" s="455"/>
+      <c r="C9" s="461"/>
+      <c r="D9" s="458"/>
       <c r="E9" s="386" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F9" s="223">
         <v>160</v>
@@ -21889,17 +21889,17 @@
         <v>160</v>
       </c>
       <c r="J9" s="119"/>
-      <c r="L9" s="448"/>
-      <c r="M9" s="448"/>
-      <c r="N9" s="448"/>
+      <c r="L9" s="467"/>
+      <c r="M9" s="467"/>
+      <c r="N9" s="467"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="352"/>
-      <c r="B10" s="450"/>
-      <c r="C10" s="453"/>
-      <c r="D10" s="455"/>
+      <c r="B10" s="455"/>
+      <c r="C10" s="461"/>
+      <c r="D10" s="458"/>
       <c r="E10" s="387" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F10" s="223">
         <v>190</v>
@@ -21913,17 +21913,17 @@
         <v>190</v>
       </c>
       <c r="J10" s="119"/>
-      <c r="L10" s="448"/>
-      <c r="M10" s="448"/>
-      <c r="N10" s="448"/>
+      <c r="L10" s="467"/>
+      <c r="M10" s="467"/>
+      <c r="N10" s="467"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="352"/>
-      <c r="B11" s="450"/>
-      <c r="C11" s="454"/>
-      <c r="D11" s="456"/>
+      <c r="B11" s="455"/>
+      <c r="C11" s="462"/>
+      <c r="D11" s="459"/>
       <c r="E11" s="386" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F11" s="223">
         <v>210</v>
@@ -21937,21 +21937,21 @@
         <v>210</v>
       </c>
       <c r="J11" s="119"/>
-      <c r="L11" s="448"/>
-      <c r="M11" s="448"/>
-      <c r="N11" s="448"/>
+      <c r="L11" s="467"/>
+      <c r="M11" s="467"/>
+      <c r="N11" s="467"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="352"/>
-      <c r="B12" s="451"/>
+      <c r="B12" s="456"/>
       <c r="C12" s="222" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E12" s="386" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F12" s="223">
         <v>40</v>
@@ -21965,23 +21965,23 @@
         <v>40</v>
       </c>
       <c r="J12" s="119"/>
-      <c r="L12" s="448"/>
-      <c r="M12" s="448"/>
-      <c r="N12" s="448"/>
+      <c r="L12" s="467"/>
+      <c r="M12" s="467"/>
+      <c r="N12" s="467"/>
     </row>
     <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="352"/>
-      <c r="B13" s="449" t="s">
+      <c r="B13" s="454" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="452" t="s">
+      <c r="C13" s="460" t="s">
         <v>104</v>
       </c>
       <c r="D13" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="E13" s="386" t="s">
         <v>512</v>
-      </c>
-      <c r="E13" s="386" t="s">
-        <v>513</v>
       </c>
       <c r="F13" s="223">
         <v>32</v>
@@ -21995,19 +21995,19 @@
         <v>32</v>
       </c>
       <c r="J13" s="119"/>
-      <c r="L13" s="448"/>
-      <c r="M13" s="448"/>
-      <c r="N13" s="448"/>
+      <c r="L13" s="467"/>
+      <c r="M13" s="467"/>
+      <c r="N13" s="467"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="352"/>
-      <c r="B14" s="450"/>
-      <c r="C14" s="453"/>
-      <c r="D14" s="463" t="s">
-        <v>514</v>
+      <c r="B14" s="455"/>
+      <c r="C14" s="461"/>
+      <c r="D14" s="457" t="s">
+        <v>513</v>
       </c>
       <c r="E14" s="386" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F14" s="223">
         <v>20</v>
@@ -22021,17 +22021,17 @@
         <v>20</v>
       </c>
       <c r="J14" s="119"/>
-      <c r="L14" s="448"/>
-      <c r="M14" s="448"/>
-      <c r="N14" s="448"/>
+      <c r="L14" s="467"/>
+      <c r="M14" s="467"/>
+      <c r="N14" s="467"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="352"/>
-      <c r="B15" s="450"/>
-      <c r="C15" s="453"/>
-      <c r="D15" s="455"/>
+      <c r="B15" s="455"/>
+      <c r="C15" s="461"/>
+      <c r="D15" s="458"/>
       <c r="E15" s="386" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F15" s="223">
         <v>28</v>
@@ -22045,17 +22045,17 @@
         <v>28</v>
       </c>
       <c r="J15" s="119"/>
-      <c r="L15" s="448"/>
-      <c r="M15" s="448"/>
-      <c r="N15" s="448"/>
+      <c r="L15" s="467"/>
+      <c r="M15" s="467"/>
+      <c r="N15" s="467"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="352"/>
-      <c r="B16" s="450"/>
-      <c r="C16" s="454"/>
-      <c r="D16" s="456"/>
+      <c r="B16" s="455"/>
+      <c r="C16" s="462"/>
+      <c r="D16" s="459"/>
       <c r="E16" s="386" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F16" s="223">
         <v>32</v>
@@ -22069,26 +22069,26 @@
         <v>32</v>
       </c>
       <c r="J16" s="119"/>
-      <c r="L16" s="448"/>
-      <c r="M16" s="448"/>
-      <c r="N16" s="448"/>
+      <c r="L16" s="467"/>
+      <c r="M16" s="467"/>
+      <c r="N16" s="467"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="437" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="450"/>
+      <c r="B17" s="455"/>
       <c r="C17" s="222" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E17" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G17" s="272"/>
       <c r="H17" s="222" t="s">
@@ -22099,24 +22099,24 @@
         <v>keine</v>
       </c>
       <c r="J17" s="119"/>
-      <c r="L17" s="448"/>
-      <c r="M17" s="448"/>
-      <c r="N17" s="448"/>
+      <c r="L17" s="467"/>
+      <c r="M17" s="467"/>
+      <c r="N17" s="467"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="437"/>
-      <c r="B18" s="450"/>
+      <c r="B18" s="455"/>
       <c r="C18" s="222" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D18" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E18" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F18" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G18" s="272"/>
       <c r="H18" s="222" t="s">
@@ -22127,24 +22127,24 @@
         <v>keine</v>
       </c>
       <c r="J18" s="119"/>
-      <c r="L18" s="448"/>
-      <c r="M18" s="448"/>
-      <c r="N18" s="448"/>
+      <c r="L18" s="467"/>
+      <c r="M18" s="467"/>
+      <c r="N18" s="467"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="437"/>
-      <c r="B19" s="451"/>
+      <c r="B19" s="456"/>
       <c r="C19" s="222" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D19" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E19" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F19" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G19" s="272"/>
       <c r="H19" s="222" t="s">
@@ -22155,39 +22155,39 @@
         <v>keine</v>
       </c>
       <c r="J19" s="119"/>
-      <c r="L19" s="448"/>
-      <c r="M19" s="448"/>
-      <c r="N19" s="448"/>
+      <c r="L19" s="467"/>
+      <c r="M19" s="467"/>
+      <c r="N19" s="467"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="352"/>
       <c r="B20" s="378"/>
       <c r="C20" s="380"/>
-      <c r="D20" s="464" t="s">
-        <v>518</v>
-      </c>
-      <c r="E20" s="465"/>
+      <c r="D20" s="463" t="s">
+        <v>517</v>
+      </c>
+      <c r="E20" s="464"/>
       <c r="F20" s="381"/>
       <c r="G20" s="382"/>
       <c r="H20" s="379"/>
       <c r="I20" s="307"/>
       <c r="J20" s="119"/>
-      <c r="L20" s="448"/>
-      <c r="M20" s="448"/>
-      <c r="N20" s="448"/>
+      <c r="L20" s="467"/>
+      <c r="M20" s="467"/>
+      <c r="N20" s="467"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="352"/>
-      <c r="B21" s="449" t="s">
+      <c r="B21" s="454" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="452" t="s">
+      <c r="C21" s="460" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="466" t="s">
-        <v>515</v>
-      </c>
-      <c r="E21" s="467"/>
+      <c r="D21" s="465" t="s">
+        <v>514</v>
+      </c>
+      <c r="E21" s="466"/>
       <c r="F21" s="386">
         <v>64</v>
       </c>
@@ -22200,18 +22200,18 @@
         <v>64</v>
       </c>
       <c r="J21" s="119"/>
-      <c r="L21" s="448"/>
-      <c r="M21" s="448"/>
-      <c r="N21" s="448"/>
+      <c r="L21" s="467"/>
+      <c r="M21" s="467"/>
+      <c r="N21" s="467"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="352"/>
-      <c r="B22" s="450"/>
-      <c r="C22" s="453"/>
-      <c r="D22" s="466" t="s">
-        <v>516</v>
-      </c>
-      <c r="E22" s="467"/>
+      <c r="B22" s="455"/>
+      <c r="C22" s="461"/>
+      <c r="D22" s="465" t="s">
+        <v>515</v>
+      </c>
+      <c r="E22" s="466"/>
       <c r="F22" s="386">
         <v>84</v>
       </c>
@@ -22225,18 +22225,18 @@
       </c>
       <c r="J22" s="119"/>
       <c r="K22" s="383"/>
-      <c r="L22" s="448"/>
-      <c r="M22" s="448"/>
-      <c r="N22" s="448"/>
+      <c r="L22" s="467"/>
+      <c r="M22" s="467"/>
+      <c r="N22" s="467"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="352"/>
-      <c r="B23" s="451"/>
-      <c r="C23" s="454"/>
-      <c r="D23" s="466" t="s">
-        <v>517</v>
-      </c>
-      <c r="E23" s="467"/>
+      <c r="B23" s="456"/>
+      <c r="C23" s="462"/>
+      <c r="D23" s="465" t="s">
+        <v>516</v>
+      </c>
+      <c r="E23" s="466"/>
       <c r="F23" s="386">
         <v>100</v>
       </c>
@@ -22249,9 +22249,9 @@
         <v>100</v>
       </c>
       <c r="J23" s="119"/>
-      <c r="L23" s="448"/>
-      <c r="M23" s="448"/>
-      <c r="N23" s="448"/>
+      <c r="L23" s="467"/>
+      <c r="M23" s="467"/>
+      <c r="N23" s="467"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="352"/>
@@ -22261,10 +22261,10 @@
       <c r="C24" s="369" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="466" t="s">
-        <v>519</v>
-      </c>
-      <c r="E24" s="467"/>
+      <c r="D24" s="465" t="s">
+        <v>518</v>
+      </c>
+      <c r="E24" s="466"/>
       <c r="F24" s="388">
         <v>3.6</v>
       </c>
@@ -22277,9 +22277,9 @@
         <v>3.6</v>
       </c>
       <c r="J24" s="119"/>
-      <c r="L24" s="448"/>
-      <c r="M24" s="448"/>
-      <c r="N24" s="448"/>
+      <c r="L24" s="467"/>
+      <c r="M24" s="467"/>
+      <c r="N24" s="467"/>
     </row>
     <row r="25" spans="1:14" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25" s="353"/>
@@ -22290,10 +22290,10 @@
         <v>99</v>
       </c>
       <c r="D25" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E25" s="223" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F25" s="224">
         <v>60</v>
@@ -22307,9 +22307,9 @@
         <v>60</v>
       </c>
       <c r="J25" s="191"/>
-      <c r="L25" s="448"/>
-      <c r="M25" s="448"/>
-      <c r="N25" s="448"/>
+      <c r="L25" s="467"/>
+      <c r="M25" s="467"/>
+      <c r="N25" s="467"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="119"/>
@@ -22368,7 +22368,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="196"/>
       <c r="B31" s="293" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C31" s="339"/>
       <c r="D31" s="339"/>
@@ -22453,7 +22453,7 @@
         <v>0.41399999999999998</v>
       </c>
       <c r="J35" s="199" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K35" s="254"/>
     </row>
@@ -22477,7 +22477,7 @@
         <v>0.59</v>
       </c>
       <c r="J36" s="199" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K36" s="254"/>
     </row>
@@ -22500,7 +22500,7 @@
       <c r="K37" s="254"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="459"/>
+      <c r="A38" s="450"/>
       <c r="B38" s="212" t="s">
         <v>48</v>
       </c>
@@ -22519,12 +22519,12 @@
         <v>1.6719999999999999</v>
       </c>
       <c r="J38" s="199" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K38" s="254"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="459"/>
+      <c r="A39" s="450"/>
       <c r="B39" s="212" t="s">
         <v>49</v>
       </c>
@@ -22543,7 +22543,7 @@
         <v>1.788</v>
       </c>
       <c r="J39" s="199" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K39" s="254"/>
     </row>
@@ -22567,7 +22567,7 @@
         <v>1.3</v>
       </c>
       <c r="J40" s="199" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K40" s="254"/>
     </row>
@@ -22614,15 +22614,15 @@
     </row>
     <row r="44" spans="1:11" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="460" t="s">
+      <c r="B44" s="451" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="461"/>
-      <c r="D44" s="461"/>
-      <c r="E44" s="461"/>
-      <c r="F44" s="461"/>
-      <c r="G44" s="461"/>
-      <c r="H44" s="462"/>
+      <c r="C44" s="452"/>
+      <c r="D44" s="452"/>
+      <c r="E44" s="452"/>
+      <c r="F44" s="452"/>
+      <c r="G44" s="452"/>
+      <c r="H44" s="453"/>
       <c r="I44" s="308" t="s">
         <v>110</v>
       </c>
@@ -22667,7 +22667,7 @@
         <v>860</v>
       </c>
       <c r="J46" s="199" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K46" s="254"/>
     </row>
@@ -22775,10 +22775,10 @@
     </row>
     <row r="53" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="193"/>
-      <c r="B53" s="457" t="s">
-        <v>400</v>
-      </c>
-      <c r="C53" s="458"/>
+      <c r="B53" s="448" t="s">
+        <v>399</v>
+      </c>
+      <c r="C53" s="449"/>
       <c r="D53" s="368"/>
       <c r="E53" s="368"/>
       <c r="F53" s="218">
@@ -22828,6 +22828,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="L5:N25"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D8:D11"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B44:H44"/>
@@ -22842,11 +22847,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="L5:N25"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D8:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="K35">
     <cfRule type="expression" dxfId="14" priority="10">
@@ -22930,7 +22930,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23344,7 +23344,7 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
@@ -23361,7 +23361,7 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
+      <c r="A47" s="391"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -23422,7 +23422,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -23486,7 +23486,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23504,7 +23504,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
+      <c r="A61" s="391"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23520,7 +23520,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
+      <c r="A62" s="391"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23622,7 +23622,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24089,7 +24089,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
@@ -24106,7 +24106,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
+      <c r="A47" s="391"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -24174,7 +24174,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -24239,7 +24239,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24257,7 +24257,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
+      <c r="A61" s="391"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24273,7 +24273,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
+      <c r="A62" s="391"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24382,7 +24382,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24849,7 +24849,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
@@ -24866,7 +24866,7 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
+      <c r="A47" s="391"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -24934,7 +24934,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -24999,7 +24999,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="391" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -25017,7 +25017,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
+      <c r="A61" s="391"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -25033,7 +25033,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
+      <c r="A62" s="391"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -25120,12 +25120,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25358,20 +25360,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25396,18 +25405,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/B2 - LZK-Rechner LNF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{91E35081-D1C7-4439-AB28-1F61A1A8072A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D9A87CE8-C110-4C1E-AC21-1873A7D644F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780DE367-EAAD-4AA0-93F7-09897E270BEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12699,7 +12699,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10143914" y="2432685"/>
+          <a:off x="10471574" y="2432685"/>
           <a:ext cx="1631979" cy="972820"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
@@ -19217,7 +19217,7 @@
     <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
     <col min="5" max="9" width="16.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="3.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.109375" style="7" customWidth="1"/>
@@ -19466,8 +19466,8 @@
         <v>Art der Beschaffung wählen in:</v>
       </c>
       <c r="D14" s="166" t="str">
-        <f>IF(ISBLANK(FinArt), "Input_Projekt", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
-        <v>Input_Projekt</v>
+        <f>IF(ISBLANK(FinArt), "Input_Beschaffung", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
+        <v>Input_Beschaffung</v>
       </c>
       <c r="E14" s="142"/>
       <c r="F14" s="142"/>
@@ -25120,17 +25120,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -25359,7 +25348,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -25368,24 +25357,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25404,10 +25387,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780DE367-EAAD-4AA0-93F7-09897E270BEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C29AC8D-A070-41C8-A966-250254372D3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11124" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="27" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <definedName name="Zusatzinfo5">Eingabe_Angebotswerte!$I$12</definedName>
     <definedName name="Zustaendig">Input_Beschaffung!$C$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2660,9 +2660,6 @@
     <t>UBA (2024b)</t>
   </si>
   <si>
-    <t>https://www.umweltbundesamt.de/sites/default/files/medien/11850/publikationen/23_2024_cc_strommix_07_2024.pdf</t>
-  </si>
-  <si>
     <t>Entwicklung der spezifischen Treibhausgas-Emissionen des deutschen Strommix in den Jahren 1990 - 2023</t>
   </si>
   <si>
@@ -3099,9 +3096,6 @@
     <t>N1-I bis N1-III</t>
   </si>
   <si>
-    <t>Lebenszykluskosten-Rechner für leichte Nutzfahrzeuge (LNF) - beispielhaft mit Daten befüllt</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Mit dem vorliegenden Excel-Tool können die Lebenszykluskosten (LZK) von leichten Nutzfahrzeugen (LNF) berechnet werden. Der LZK-Rechner wurde vom ifeu entwickelt. Fördergeber waren die Deutsche Bundesstiftung Umwelt sowie die Bundesländer Berlin und Brandenburg.
 Das Tool richtet sich in erster Linie an Personen im Beschaffungsprozess, kann aber auch anderen Nutzendengruppen wie Fachexpert*innen, OEMs oder Autohäusern dienlich sein. Bei komplexen Beschaffungen wird die Zusammenarbeit mit Fachexpert*innen empfohlen, die beim Befüllen der gefragten Daten unterstützen.
@@ -3456,6 +3450,12 @@
       </rPr>
       <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
     </r>
+  </si>
+  <si>
+    <t>Lebenszykluskosten-Rechner für leichte Nutzfahrzeuge (LNF)</t>
+  </si>
+  <si>
+    <t>https://www.umweltbundesamt.de/publikationen/entwicklung-der-spezifischen-treibhausgas-10</t>
   </si>
 </sst>
 </file>
@@ -4831,7 +4831,7 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="474">
+  <cellXfs count="473">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5454,9 +5454,6 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -12699,8 +12696,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10471574" y="2432685"/>
-          <a:ext cx="1631979" cy="972820"/>
+          <a:off x="10479194" y="2392680"/>
+          <a:ext cx="1630074" cy="969010"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -14294,7 +14291,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>519</v>
+        <v>608</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -14304,7 +14301,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14326,17 +14323,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="394" t="s">
-        <v>520</v>
-      </c>
-      <c r="C5" s="394"/>
-      <c r="D5" s="394"/>
-      <c r="E5" s="394"/>
-      <c r="F5" s="394"/>
-      <c r="G5" s="394"/>
-      <c r="H5" s="394"/>
-      <c r="I5" s="394"/>
-      <c r="J5" s="394"/>
+      <c r="B5" s="393" t="s">
+        <v>518</v>
+      </c>
+      <c r="C5" s="393"/>
+      <c r="D5" s="393"/>
+      <c r="E5" s="393"/>
+      <c r="F5" s="393"/>
+      <c r="G5" s="393"/>
+      <c r="H5" s="393"/>
+      <c r="I5" s="393"/>
+      <c r="J5" s="393"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14374,13 +14371,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="395" t="s">
+      <c r="F9" s="394" t="s">
         <v>402</v>
       </c>
-      <c r="G9" s="395"/>
-      <c r="H9" s="395"/>
-      <c r="I9" s="395"/>
-      <c r="J9" s="395"/>
+      <c r="G9" s="394"/>
+      <c r="H9" s="394"/>
+      <c r="I9" s="394"/>
+      <c r="J9" s="394"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14394,31 +14391,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="396" t="s">
-        <v>417</v>
-      </c>
-      <c r="G11" s="397"/>
-      <c r="H11" s="397"/>
-      <c r="I11" s="397"/>
-      <c r="J11" s="397"/>
+      <c r="F11" s="395" t="s">
+        <v>416</v>
+      </c>
+      <c r="G11" s="396"/>
+      <c r="H11" s="396"/>
+      <c r="I11" s="396"/>
+      <c r="J11" s="396"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="397"/>
-      <c r="G12" s="397"/>
-      <c r="H12" s="397"/>
-      <c r="I12" s="397"/>
-      <c r="J12" s="397"/>
+      <c r="F12" s="396"/>
+      <c r="G12" s="396"/>
+      <c r="H12" s="396"/>
+      <c r="I12" s="396"/>
+      <c r="J12" s="396"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="397"/>
-      <c r="G13" s="397"/>
-      <c r="H13" s="397"/>
-      <c r="I13" s="397"/>
-      <c r="J13" s="397"/>
+      <c r="F13" s="396"/>
+      <c r="G13" s="396"/>
+      <c r="H13" s="396"/>
+      <c r="I13" s="396"/>
+      <c r="J13" s="396"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14432,22 +14429,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="398" t="s">
+      <c r="F15" s="397" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="399"/>
-      <c r="H15" s="399"/>
-      <c r="I15" s="399"/>
-      <c r="J15" s="399"/>
+      <c r="G15" s="398"/>
+      <c r="H15" s="398"/>
+      <c r="I15" s="398"/>
+      <c r="J15" s="398"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="399"/>
-      <c r="G16" s="399"/>
-      <c r="H16" s="399"/>
-      <c r="I16" s="399"/>
-      <c r="J16" s="399"/>
+      <c r="F16" s="398"/>
+      <c r="G16" s="398"/>
+      <c r="H16" s="398"/>
+      <c r="I16" s="398"/>
+      <c r="J16" s="398"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14461,13 +14458,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="400" t="s">
+      <c r="F18" s="399" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="401"/>
-      <c r="H18" s="401"/>
-      <c r="I18" s="401"/>
-      <c r="J18" s="401"/>
+      <c r="G18" s="400"/>
+      <c r="H18" s="400"/>
+      <c r="I18" s="400"/>
+      <c r="J18" s="400"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14481,31 +14478,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="402" t="s">
+      <c r="F20" s="401" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="402"/>
-      <c r="H20" s="402"/>
-      <c r="I20" s="402"/>
-      <c r="J20" s="402"/>
+      <c r="G20" s="401"/>
+      <c r="H20" s="401"/>
+      <c r="I20" s="401"/>
+      <c r="J20" s="401"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="402"/>
-      <c r="G21" s="402"/>
-      <c r="H21" s="402"/>
-      <c r="I21" s="402"/>
-      <c r="J21" s="402"/>
+      <c r="F21" s="401"/>
+      <c r="G21" s="401"/>
+      <c r="H21" s="401"/>
+      <c r="I21" s="401"/>
+      <c r="J21" s="401"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="402"/>
-      <c r="G22" s="402"/>
-      <c r="H22" s="402"/>
-      <c r="I22" s="402"/>
-      <c r="J22" s="402"/>
+      <c r="F22" s="401"/>
+      <c r="G22" s="401"/>
+      <c r="H22" s="401"/>
+      <c r="I22" s="401"/>
+      <c r="J22" s="401"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14519,22 +14516,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="403" t="s">
+      <c r="F24" s="402" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="403"/>
-      <c r="H24" s="403"/>
-      <c r="I24" s="403"/>
-      <c r="J24" s="403"/>
+      <c r="G24" s="402"/>
+      <c r="H24" s="402"/>
+      <c r="I24" s="402"/>
+      <c r="J24" s="402"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="403"/>
-      <c r="G25" s="403"/>
-      <c r="H25" s="403"/>
-      <c r="I25" s="403"/>
-      <c r="J25" s="403"/>
+      <c r="F25" s="402"/>
+      <c r="G25" s="402"/>
+      <c r="H25" s="402"/>
+      <c r="I25" s="402"/>
+      <c r="J25" s="402"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14548,49 +14545,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="393"/>
-      <c r="G27" s="393"/>
-      <c r="H27" s="393"/>
-      <c r="I27" s="393"/>
-      <c r="J27" s="393"/>
+      <c r="F27" s="392"/>
+      <c r="G27" s="392"/>
+      <c r="H27" s="392"/>
+      <c r="I27" s="392"/>
+      <c r="J27" s="392"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="404" t="s">
-        <v>418</v>
-      </c>
-      <c r="G28" s="404"/>
-      <c r="H28" s="404"/>
-      <c r="I28" s="404"/>
-      <c r="J28" s="404"/>
+      <c r="F28" s="403" t="s">
+        <v>417</v>
+      </c>
+      <c r="G28" s="403"/>
+      <c r="H28" s="403"/>
+      <c r="I28" s="403"/>
+      <c r="J28" s="403"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="404"/>
-      <c r="G29" s="404"/>
-      <c r="H29" s="404"/>
-      <c r="I29" s="404"/>
-      <c r="J29" s="404"/>
+      <c r="F29" s="403"/>
+      <c r="G29" s="403"/>
+      <c r="H29" s="403"/>
+      <c r="I29" s="403"/>
+      <c r="J29" s="403"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="404"/>
-      <c r="G30" s="404"/>
-      <c r="H30" s="404"/>
-      <c r="I30" s="404"/>
-      <c r="J30" s="404"/>
+      <c r="F30" s="403"/>
+      <c r="G30" s="403"/>
+      <c r="H30" s="403"/>
+      <c r="I30" s="403"/>
+      <c r="J30" s="403"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="392"/>
-      <c r="G31" s="392"/>
-      <c r="H31" s="392"/>
-      <c r="I31" s="392"/>
-      <c r="J31" s="392"/>
+      <c r="F31" s="391"/>
+      <c r="G31" s="391"/>
+      <c r="H31" s="391"/>
+      <c r="I31" s="391"/>
+      <c r="J31" s="391"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14639,15 +14636,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="392" t="s">
+      <c r="D36" s="391" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="392"/>
-      <c r="F36" s="392"/>
-      <c r="G36" s="392"/>
-      <c r="H36" s="392"/>
-      <c r="I36" s="392"/>
-      <c r="J36" s="392"/>
+      <c r="E36" s="391"/>
+      <c r="F36" s="391"/>
+      <c r="G36" s="391"/>
+      <c r="H36" s="391"/>
+      <c r="I36" s="391"/>
+      <c r="J36" s="391"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14663,24 +14660,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="393" t="s">
+      <c r="D38" s="392" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="393"/>
-      <c r="F38" s="393"/>
-      <c r="G38" s="393"/>
-      <c r="H38" s="393"/>
-      <c r="I38" s="393"/>
-      <c r="J38" s="393"/>
+      <c r="E38" s="392"/>
+      <c r="F38" s="392"/>
+      <c r="G38" s="392"/>
+      <c r="H38" s="392"/>
+      <c r="I38" s="392"/>
+      <c r="J38" s="392"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="393"/>
-      <c r="E39" s="393"/>
-      <c r="F39" s="393"/>
-      <c r="G39" s="393"/>
-      <c r="H39" s="393"/>
-      <c r="I39" s="393"/>
-      <c r="J39" s="393"/>
+      <c r="D39" s="392"/>
+      <c r="E39" s="392"/>
+      <c r="F39" s="392"/>
+      <c r="G39" s="392"/>
+      <c r="H39" s="392"/>
+      <c r="I39" s="392"/>
+      <c r="J39" s="392"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14698,15 +14695,15 @@
         <v>9</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="390" t="s">
+      <c r="D41" s="389" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="390"/>
-      <c r="F41" s="390"/>
-      <c r="G41" s="390"/>
-      <c r="H41" s="390"/>
-      <c r="I41" s="390"/>
-      <c r="J41" s="390"/>
+      <c r="E41" s="389"/>
+      <c r="F41" s="389"/>
+      <c r="G41" s="389"/>
+      <c r="H41" s="389"/>
+      <c r="I41" s="389"/>
+      <c r="J41" s="389"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14720,30 +14717,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="391" t="s">
+      <c r="B43" s="390" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="392" t="s">
+      <c r="D43" s="391" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="392"/>
-      <c r="F43" s="392"/>
-      <c r="G43" s="392"/>
-      <c r="H43" s="392"/>
-      <c r="I43" s="392"/>
-      <c r="J43" s="392"/>
+      <c r="E43" s="391"/>
+      <c r="F43" s="391"/>
+      <c r="G43" s="391"/>
+      <c r="H43" s="391"/>
+      <c r="I43" s="391"/>
+      <c r="J43" s="391"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="391"/>
+      <c r="B44" s="390"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="392"/>
-      <c r="E44" s="392"/>
-      <c r="F44" s="392"/>
-      <c r="G44" s="392"/>
-      <c r="H44" s="392"/>
-      <c r="I44" s="392"/>
-      <c r="J44" s="392"/>
+      <c r="D44" s="391"/>
+      <c r="E44" s="391"/>
+      <c r="F44" s="391"/>
+      <c r="G44" s="391"/>
+      <c r="H44" s="391"/>
+      <c r="I44" s="391"/>
+      <c r="J44" s="391"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14755,17 +14752,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="392" t="s">
-        <v>609</v>
-      </c>
-      <c r="C46" s="392"/>
-      <c r="D46" s="392"/>
-      <c r="E46" s="392"/>
-      <c r="F46" s="392"/>
-      <c r="G46" s="392"/>
-      <c r="H46" s="392"/>
-      <c r="I46" s="392"/>
-      <c r="J46" s="392"/>
+      <c r="B46" s="391" t="s">
+        <v>607</v>
+      </c>
+      <c r="C46" s="391"/>
+      <c r="D46" s="391"/>
+      <c r="E46" s="391"/>
+      <c r="F46" s="391"/>
+      <c r="G46" s="391"/>
+      <c r="H46" s="391"/>
+      <c r="I46" s="391"/>
+      <c r="J46" s="391"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14800,17 +14797,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="392" t="s">
+      <c r="B50" s="391" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="392"/>
-      <c r="D50" s="392"/>
-      <c r="E50" s="392"/>
-      <c r="F50" s="392"/>
-      <c r="G50" s="392"/>
-      <c r="H50" s="392"/>
-      <c r="I50" s="392"/>
-      <c r="J50" s="392"/>
+      <c r="C50" s="391"/>
+      <c r="D50" s="391"/>
+      <c r="E50" s="391"/>
+      <c r="F50" s="391"/>
+      <c r="G50" s="391"/>
+      <c r="H50" s="391"/>
+      <c r="I50" s="391"/>
+      <c r="J50" s="391"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14931,7 +14928,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15084,7 +15081,7 @@
       <c r="B18" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -15096,7 +15093,7 @@
       <c r="B19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -15110,7 +15107,7 @@
       <c r="B20" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP4/C18</f>
         <v>0</v>
       </c>
@@ -15124,7 +15121,7 @@
       <c r="B21" s="186" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -15133,13 +15130,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -15150,9 +15147,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -15193,7 +15190,7 @@
       <c r="B28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,8,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -15207,7 +15204,7 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -15221,7 +15218,7 @@
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -15253,7 +15250,7 @@
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -15267,7 +15264,7 @@
       <c r="B34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -15281,7 +15278,7 @@
       <c r="B35" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -15295,7 +15292,7 @@
       <c r="B36" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -15309,7 +15306,7 @@
       <c r="B37" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -15341,7 +15338,7 @@
       <c r="B40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -15355,7 +15352,7 @@
       <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -15398,13 +15395,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -15415,9 +15412,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15431,7 +15428,7 @@
       <c r="B48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C48" s="279" t="e">
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15468,7 +15465,7 @@
       <c r="B54" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
@@ -15479,13 +15476,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C55" s="283">
+        <v>430</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -15499,7 +15496,7 @@
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15512,7 +15509,7 @@
       <c r="B57" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15525,7 +15522,7 @@
       <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15535,10 +15532,10 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="333" t="s">
+      <c r="B59" s="332" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="334" t="e">
+      <c r="C59" s="333" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
@@ -15548,50 +15545,50 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -15601,7 +15598,7 @@
       <c r="B63" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="284" t="e">
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15623,7 +15620,7 @@
       <c r="B65" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="285" t="e">
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15635,7 +15632,7 @@
       <c r="B66" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15691,7 +15688,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15847,7 +15844,7 @@
       <c r="B18" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -15859,7 +15856,7 @@
       <c r="B19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -15873,7 +15870,7 @@
       <c r="B20" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP5/C18</f>
         <v>0</v>
       </c>
@@ -15887,7 +15884,7 @@
       <c r="B21" s="186" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -15896,13 +15893,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -15913,9 +15910,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -15956,7 +15953,7 @@
       <c r="B28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,8,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -15970,7 +15967,7 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -15984,7 +15981,7 @@
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -16017,7 +16014,7 @@
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -16031,7 +16028,7 @@
       <c r="B34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -16045,7 +16042,7 @@
       <c r="B35" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -16059,7 +16056,7 @@
       <c r="B36" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -16073,7 +16070,7 @@
       <c r="B37" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -16105,7 +16102,7 @@
       <c r="B40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -16119,7 +16116,7 @@
       <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -16162,13 +16159,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -16179,9 +16176,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -16195,7 +16192,7 @@
       <c r="B48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C48" s="279" t="e">
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -16232,7 +16229,7 @@
       <c r="B54" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
@@ -16243,13 +16240,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C55" s="283">
+        <v>430</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -16263,7 +16260,7 @@
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -16276,7 +16273,7 @@
       <c r="B57" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -16289,7 +16286,7 @@
       <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -16299,63 +16296,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="330" t="e">
+      <c r="C59" s="329" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -16365,7 +16362,7 @@
       <c r="B63" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="284" t="e">
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
@@ -16387,7 +16384,7 @@
       <c r="B65" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="285" t="e">
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -16399,7 +16396,7 @@
       <c r="B66" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -16458,7 +16455,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16480,7 +16477,7 @@
       <c r="B7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="302">
+      <c r="C7" s="301">
         <v>74.027000000000001</v>
       </c>
       <c r="D7" s="10">
@@ -16494,7 +16491,7 @@
       <c r="B8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="302">
+      <c r="C8" s="301">
         <v>72.787000000000006</v>
       </c>
       <c r="D8" s="10">
@@ -16508,7 +16505,7 @@
       <c r="B9" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="302">
+      <c r="C9" s="301">
         <v>56.220999999999997</v>
       </c>
       <c r="D9" s="10">
@@ -16520,7 +16517,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16550,15 +16547,15 @@
       <c r="B14" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="472" t="s">
+      <c r="C14" s="471" t="s">
         <v>165</v>
       </c>
-      <c r="D14" s="472"/>
-      <c r="E14" s="473" t="s">
+      <c r="D14" s="471"/>
+      <c r="E14" s="472" t="s">
         <v>166</v>
       </c>
-      <c r="F14" s="473"/>
-      <c r="G14" s="304"/>
+      <c r="F14" s="472"/>
+      <c r="G14" s="303"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
@@ -16612,7 +16609,7 @@
       <c r="D17" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E17" s="303">
+      <c r="E17" s="302">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
@@ -16622,14 +16619,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16651,7 +16648,7 @@
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16680,7 +16677,7 @@
       <c r="C23" s="58">
         <v>0</v>
       </c>
-      <c r="D23" s="299" t="e">
+      <c r="D23" s="298" t="e">
         <f>SUMIFS(J24:AE24, J23:AE23, "&gt;=" &amp; Anschaffungsjahr, J23:AE23,  "&lt;" &amp; Anschaffungsjahr + ROUND(Haltedauer, 0))/ROUND(Haltedauer, 0)</f>
         <v>#DIV/0!</v>
       </c>
@@ -16793,15 +16790,15 @@
         <v>172</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>446</v>
-      </c>
-      <c r="J24" s="300">
+        <v>445</v>
+      </c>
+      <c r="J24" s="299">
         <v>445</v>
       </c>
       <c r="K24" s="96">
         <v>408</v>
       </c>
-      <c r="L24" s="301">
+      <c r="L24" s="300">
         <v>371</v>
       </c>
       <c r="M24" s="96">
@@ -16816,7 +16813,7 @@
       <c r="P24" s="96">
         <v>211.8</v>
       </c>
-      <c r="Q24" s="301">
+      <c r="Q24" s="300">
         <v>172</v>
       </c>
       <c r="R24" s="96">
@@ -16831,7 +16828,7 @@
       <c r="U24" s="96">
         <v>119.2</v>
       </c>
-      <c r="V24" s="301">
+      <c r="V24" s="300">
         <v>106</v>
       </c>
       <c r="W24" s="96">
@@ -16846,7 +16843,7 @@
       <c r="Z24" s="96">
         <v>82</v>
       </c>
-      <c r="AA24" s="301">
+      <c r="AA24" s="300">
         <v>76</v>
       </c>
       <c r="AB24" s="136">
@@ -16876,7 +16873,7 @@
       <c r="AJ24" s="136">
         <v>79.599999999999994</v>
       </c>
-      <c r="AK24" s="301">
+      <c r="AK24" s="300">
         <v>80</v>
       </c>
     </row>
@@ -16972,12 +16969,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16993,12 +16990,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -17016,7 +17013,7 @@
         <v>401</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -17024,7 +17021,7 @@
         <v>192</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -17032,7 +17029,7 @@
         <v>193</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -17040,7 +17037,7 @@
         <v>194</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -17048,7 +17045,7 @@
         <v>28</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -17056,7 +17053,7 @@
         <v>195</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -17064,23 +17061,23 @@
         <v>196</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -17088,15 +17085,15 @@
         <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17104,7 +17101,7 @@
         <v>198</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
@@ -17192,7 +17189,7 @@
         <v>219</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
@@ -17200,7 +17197,7 @@
         <v>221</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
@@ -17208,7 +17205,7 @@
         <v>223</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
@@ -17216,7 +17213,7 @@
         <v>225</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
@@ -17224,7 +17221,7 @@
         <v>227</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
@@ -17309,7 +17306,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>250</v>
@@ -17317,7 +17314,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>252</v>
@@ -17325,7 +17322,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>254</v>
@@ -17333,7 +17330,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>256</v>
@@ -17341,7 +17338,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>258</v>
@@ -17709,146 +17706,146 @@
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17896,7 +17893,7 @@
         <v>366</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
@@ -17904,7 +17901,7 @@
         <v>349</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17912,7 +17909,7 @@
         <v>350</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
@@ -17920,7 +17917,7 @@
         <v>351</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
@@ -17928,71 +17925,71 @@
         <v>352</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -18000,63 +17997,63 @@
         <v>353</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -18064,7 +18061,7 @@
         <v>354</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -18072,7 +18069,7 @@
         <v>355</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -18080,7 +18077,7 @@
         <v>181</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -18088,7 +18085,7 @@
         <v>356</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -18096,7 +18093,7 @@
         <v>361</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -18104,7 +18101,7 @@
         <v>182</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -18112,7 +18109,7 @@
         <v>357</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -18120,7 +18117,7 @@
         <v>362</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -18128,7 +18125,7 @@
         <v>183</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
@@ -18136,7 +18133,7 @@
         <v>358</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -18144,7 +18141,7 @@
         <v>363</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
@@ -18152,7 +18149,7 @@
         <v>185</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
@@ -18160,7 +18157,7 @@
         <v>359</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
@@ -18168,7 +18165,7 @@
         <v>364</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
@@ -18176,7 +18173,7 @@
         <v>186</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
@@ -18184,7 +18181,7 @@
         <v>360</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
@@ -18192,7 +18189,7 @@
         <v>365</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
@@ -18200,7 +18197,7 @@
         <v>367</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
@@ -18208,7 +18205,7 @@
         <v>368</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
@@ -18216,7 +18213,7 @@
         <v>369</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
@@ -18224,7 +18221,7 @@
         <v>370</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
@@ -18240,7 +18237,7 @@
         <v>373</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
@@ -18248,31 +18245,31 @@
         <v>374</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -18404,7 +18401,7 @@
         <v>182</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18468,7 +18465,7 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18477,17 +18474,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="5"/>
@@ -18496,32 +18493,32 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -18529,18 +18526,18 @@
       <c r="F40" s="5"/>
     </row>
     <row r="41" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B41" s="385" t="s">
+      <c r="B41" s="384" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B42" s="384" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B43" s="384" t="s">
         <v>526</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B42" s="385" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B43" s="385" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -18592,164 +18589,164 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="275" t="s">
+    <row r="4" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="274" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="274" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="275" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="274" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="274" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="275" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="274" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" s="269" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="275" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" s="274" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="276" t="s">
+        <v>379</v>
+      </c>
+      <c r="C10" s="269" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="269"/>
+      <c r="C11" s="275" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="B12" s="277" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="274" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="275" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="274" t="s">
+        <v>436</v>
+      </c>
+      <c r="C14" s="274" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="275" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="277" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="274" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C17" s="275" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="274" t="s">
+        <v>442</v>
+      </c>
+      <c r="C18" s="274" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="275" t="s">
         <v>440</v>
       </c>
-      <c r="C4" s="275" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="276" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="275" t="s">
-        <v>410</v>
-      </c>
-      <c r="C6" s="275" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="276" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="275" t="s">
-        <v>435</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="276" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="277" t="s">
-        <v>379</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="270"/>
-      <c r="C11" s="276" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="B12" s="278" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="275" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="276" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="275" t="s">
-        <v>437</v>
-      </c>
-      <c r="C14" s="275" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="276" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="278" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="275" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C17" s="276" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="275" t="s">
-        <v>443</v>
-      </c>
-      <c r="C18" s="275" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="276" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="275" t="s">
+    </row>
+    <row r="20" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="274" t="s">
         <v>386</v>
       </c>
-      <c r="C20" s="275" t="s">
+      <c r="C20" s="274" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="276" t="s">
+    <row r="21" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="275" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="275" t="s">
+    <row r="22" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="274" t="s">
+        <v>414</v>
+      </c>
+      <c r="C22" s="274" t="s">
         <v>415</v>
       </c>
-      <c r="C22" s="275" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="276" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="275" t="s">
+    </row>
+    <row r="23" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="275" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="274" t="s">
         <v>404</v>
       </c>
-      <c r="C24" s="275" t="s">
+      <c r="C24" s="274" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C25" s="276" t="s">
+    <row r="25" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C25" s="275" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="275" t="s">
+    <row r="26" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="274" t="s">
         <v>405</v>
       </c>
-      <c r="C26" s="275" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="269" t="s">
+      <c r="C26" s="274" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="275" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <hyperlinks>
@@ -18795,7 +18792,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>20</v>
@@ -18814,52 +18811,52 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C6" s="409"/>
-      <c r="D6" s="410"/>
-      <c r="E6" s="410"/>
-      <c r="F6" s="410"/>
-      <c r="G6" s="410"/>
-      <c r="H6" s="411"/>
+        <v>433</v>
+      </c>
+      <c r="C6" s="408"/>
+      <c r="D6" s="409"/>
+      <c r="E6" s="409"/>
+      <c r="F6" s="409"/>
+      <c r="G6" s="409"/>
+      <c r="H6" s="410"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="412"/>
-      <c r="D7" s="413"/>
-      <c r="E7" s="413"/>
-      <c r="F7" s="413"/>
-      <c r="G7" s="413"/>
-      <c r="H7" s="414"/>
+      <c r="C7" s="411"/>
+      <c r="D7" s="412"/>
+      <c r="E7" s="412"/>
+      <c r="F7" s="412"/>
+      <c r="G7" s="412"/>
+      <c r="H7" s="413"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="415"/>
-      <c r="D8" s="416"/>
-      <c r="E8" s="416"/>
-      <c r="F8" s="416"/>
-      <c r="G8" s="416"/>
-      <c r="H8" s="417"/>
+      <c r="C8" s="414"/>
+      <c r="D8" s="415"/>
+      <c r="E8" s="415"/>
+      <c r="F8" s="415"/>
+      <c r="G8" s="415"/>
+      <c r="H8" s="416"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="418"/>
-      <c r="D9" s="419"/>
-      <c r="E9" s="419"/>
-      <c r="F9" s="419"/>
-      <c r="G9" s="419"/>
-      <c r="H9" s="420"/>
+      <c r="C9" s="417"/>
+      <c r="D9" s="418"/>
+      <c r="E9" s="418"/>
+      <c r="F9" s="418"/>
+      <c r="G9" s="418"/>
+      <c r="H9" s="419"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="418"/>
-      <c r="D10" s="419"/>
-      <c r="E10" s="419"/>
-      <c r="F10" s="419"/>
-      <c r="G10" s="419"/>
-      <c r="H10" s="420"/>
+      <c r="C10" s="417"/>
+      <c r="D10" s="418"/>
+      <c r="E10" s="418"/>
+      <c r="F10" s="418"/>
+      <c r="G10" s="418"/>
+      <c r="H10" s="419"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -18881,26 +18878,26 @@
       <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="391" t="s">
+      <c r="A13" s="390" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="C13" s="406"/>
-      <c r="D13" s="407"/>
+        <v>557</v>
+      </c>
+      <c r="C13" s="405"/>
+      <c r="D13" s="406"/>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
       <c r="G13" s="55"/>
       <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="391"/>
+      <c r="A14" s="390"/>
       <c r="B14" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="C14" s="406"/>
-      <c r="D14" s="407"/>
+        <v>559</v>
+      </c>
+      <c r="C14" s="405"/>
+      <c r="D14" s="406"/>
       <c r="E14" s="55"/>
       <c r="F14" s="55"/>
       <c r="G14" s="55"/>
@@ -18916,7 +18913,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C16" s="152"/>
       <c r="D16" s="55" t="s">
@@ -18955,7 +18952,7 @@
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="298" t="s">
+      <c r="B20" s="297" t="s">
         <v>401</v>
       </c>
       <c r="C20" s="151"/>
@@ -18966,7 +18963,7 @@
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="297"/>
+      <c r="B21" s="296"/>
       <c r="C21" s="55"/>
       <c r="D21" s="55"/>
       <c r="E21" s="55"/>
@@ -18991,14 +18988,14 @@
       <c r="A24" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="408" t="s">
+      <c r="B24" s="407" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="405"/>
-      <c r="D24" s="405"/>
+      <c r="C24" s="404"/>
+      <c r="D24" s="404"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="408"/>
+      <c r="B25" s="407"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B26" s="176"/>
@@ -19017,7 +19014,7 @@
       <c r="E27" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F27" s="274">
+      <c r="F27" s="273">
         <f>Grunddaten!G46</f>
         <v>0</v>
       </c>
@@ -19027,7 +19024,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" s="154" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -19386,10 +19383,10 @@
       <c r="I10" s="140"/>
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
-      <c r="L10" s="432" t="s">
+      <c r="L10" s="431" t="s">
         <v>397</v>
       </c>
-      <c r="M10" s="432"/>
+      <c r="M10" s="431"/>
       <c r="N10" s="236"/>
       <c r="O10" s="164"/>
       <c r="P10" s="164"/>
@@ -19407,12 +19404,12 @@
       <c r="H11" s="141"/>
       <c r="I11" s="141"/>
       <c r="J11" s="238"/>
-      <c r="K11" s="434" t="s">
+      <c r="K11" s="433" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="434"/>
-      <c r="M11" s="434"/>
-      <c r="N11" s="434"/>
+      <c r="L11" s="433"/>
+      <c r="M11" s="433"/>
+      <c r="N11" s="433"/>
       <c r="O11" s="164"/>
       <c r="P11" s="164"/>
       <c r="Q11" s="164"/>
@@ -19429,12 +19426,12 @@
       <c r="H12" s="141"/>
       <c r="I12" s="141"/>
       <c r="J12" s="164"/>
-      <c r="K12" s="433" t="s">
+      <c r="K12" s="432" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="433"/>
-      <c r="M12" s="433"/>
-      <c r="N12" s="433"/>
+      <c r="L12" s="432"/>
+      <c r="M12" s="432"/>
+      <c r="N12" s="432"/>
       <c r="O12" s="164"/>
       <c r="P12" s="164"/>
       <c r="Q12" s="164"/>
@@ -19442,19 +19439,19 @@
     </row>
     <row r="13" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="165" t="s">
-        <v>560</v>
-      </c>
-      <c r="D13" s="384"/>
+        <v>558</v>
+      </c>
+      <c r="D13" s="383"/>
       <c r="E13" s="139"/>
       <c r="F13" s="139"/>
       <c r="G13" s="139"/>
       <c r="H13" s="139"/>
       <c r="I13" s="139"/>
       <c r="J13" s="164"/>
-      <c r="K13" s="366"/>
-      <c r="L13" s="366"/>
-      <c r="M13" s="366"/>
-      <c r="N13" s="366"/>
+      <c r="K13" s="365"/>
+      <c r="L13" s="365"/>
+      <c r="M13" s="365"/>
+      <c r="N13" s="365"/>
       <c r="O13" s="164"/>
       <c r="P13" s="164"/>
       <c r="Q13" s="164"/>
@@ -19491,11 +19488,11 @@
       <c r="D15" s="263" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="361"/>
-      <c r="F15" s="364"/>
-      <c r="G15" s="361"/>
-      <c r="H15" s="361"/>
-      <c r="I15" s="361"/>
+      <c r="E15" s="360"/>
+      <c r="F15" s="363"/>
+      <c r="G15" s="360"/>
+      <c r="H15" s="360"/>
+      <c r="I15" s="360"/>
       <c r="J15" s="264" t="s">
         <v>58</v>
       </c>
@@ -19509,21 +19506,21 @@
       <c r="R15" s="164"/>
     </row>
     <row r="16" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="431" t="s">
+      <c r="B16" s="430" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="C16" s="428" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="359" t="s">
+      <c r="D16" s="358" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="365"/>
+      <c r="E16" s="364"/>
       <c r="F16" s="257"/>
-      <c r="G16" s="363"/>
-      <c r="H16" s="363"/>
-      <c r="I16" s="362"/>
-      <c r="J16" s="360"/>
+      <c r="G16" s="362"/>
+      <c r="H16" s="362"/>
+      <c r="I16" s="361"/>
+      <c r="J16" s="359"/>
       <c r="K16" s="164"/>
       <c r="L16" s="164"/>
       <c r="M16" s="164"/>
@@ -19533,16 +19530,16 @@
       <c r="R16" s="164"/>
     </row>
     <row r="17" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="431"/>
-      <c r="C17" s="430"/>
+      <c r="B17" s="430"/>
+      <c r="C17" s="429"/>
       <c r="D17" s="166" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="357"/>
+      <c r="E17" s="356"/>
       <c r="F17" s="257"/>
       <c r="G17" s="257"/>
       <c r="H17" s="257"/>
-      <c r="I17" s="358"/>
+      <c r="I17" s="357"/>
       <c r="J17" s="164"/>
       <c r="K17" s="164"/>
       <c r="L17" s="164"/>
@@ -19554,7 +19551,7 @@
       <c r="R17" s="164"/>
     </row>
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="431"/>
+      <c r="B18" s="430"/>
       <c r="C18" s="162" t="s">
         <v>63</v>
       </c>
@@ -19577,7 +19574,7 @@
       <c r="R18" s="164"/>
     </row>
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="431"/>
+      <c r="B19" s="430"/>
       <c r="C19" s="162" t="s">
         <v>65</v>
       </c>
@@ -19603,7 +19600,7 @@
       <c r="R19" s="164"/>
     </row>
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="431"/>
+      <c r="B20" s="430"/>
       <c r="C20" s="162" t="s">
         <v>67</v>
       </c>
@@ -19626,7 +19623,7 @@
       <c r="R20" s="164"/>
     </row>
     <row r="21" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="431"/>
+      <c r="B21" s="430"/>
       <c r="C21" s="162" t="s">
         <v>68</v>
       </c>
@@ -19674,23 +19671,23 @@
       <c r="D23" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="389">
+      <c r="E23" s="388">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="389">
+      <c r="F23" s="388">
         <f>IF(AND(OR(Energie2="nicht verfügbar",COUNTIF(EnList2,Energie2)&lt;&gt;1),Antriebsart2&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="389">
+      <c r="G23" s="388">
         <f>IF(AND(OR(Energie3="nicht verfügbar",COUNTIF(EnList3,Energie3)&lt;&gt;1),Antriebsart3&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="389">
+      <c r="H23" s="388">
         <f>IF(AND(OR(Energie4="nicht verfügbar",COUNTIF(EnList4,Energie4)&lt;&gt;1),Antriebsart4&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="389">
+      <c r="I23" s="388">
         <f>IF(AND(OR(Energie5="nicht verfügbar",COUNTIF(EnList5,Energie5)&lt;&gt;1),Antriebsart5&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
@@ -19705,14 +19702,14 @@
     </row>
     <row r="24" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C24" s="77" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D24" s="228"/>
-      <c r="E24" s="389"/>
-      <c r="F24" s="389"/>
-      <c r="G24" s="389"/>
-      <c r="H24" s="389"/>
-      <c r="I24" s="389"/>
+      <c r="E24" s="388"/>
+      <c r="F24" s="388"/>
+      <c r="G24" s="388"/>
+      <c r="H24" s="388"/>
+      <c r="I24" s="388"/>
       <c r="J24" s="146"/>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
@@ -19720,11 +19717,11 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="391" t="s">
+      <c r="B25" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="331"/>
-      <c r="D25" s="322" t="s">
+      <c r="C25" s="330"/>
+      <c r="D25" s="321" t="s">
         <v>142</v>
       </c>
       <c r="E25" s="256"/>
@@ -19739,9 +19736,9 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="391"/>
-      <c r="C26" s="331"/>
-      <c r="D26" s="322" t="s">
+      <c r="B26" s="390"/>
+      <c r="C26" s="330"/>
+      <c r="D26" s="321" t="s">
         <v>142</v>
       </c>
       <c r="E26" s="256"/>
@@ -19756,9 +19753,9 @@
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="391"/>
-      <c r="C27" s="335"/>
-      <c r="D27" s="322" t="s">
+      <c r="B27" s="390"/>
+      <c r="C27" s="334"/>
+      <c r="D27" s="321" t="s">
         <v>142</v>
       </c>
       <c r="E27" s="256"/>
@@ -19776,23 +19773,23 @@
       <c r="D28" s="228" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="389">
+      <c r="E28" s="388">
         <f>IF(OR(AND(COUNT(E16:E22)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E17,E22)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E16,E18:E20)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="389">
+      <c r="F28" s="388">
         <f>IF(OR(AND(COUNT(F16:F22)&lt;7,Antriebsart2="Plug-In-Hybrid (PHEV)"),AND(COUNT(F17,F22)&lt;2,Antriebsart2="Vollelektrisch (BEV)"),AND(COUNT(F16,F18:F20)&lt;4,Antriebsart2="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="389">
+      <c r="G28" s="388">
         <f>IF(OR(AND(COUNT(G16:G22)&lt;7,Antriebsart3="Plug-In-Hybrid (PHEV)"),AND(COUNT(G17,G22)&lt;2,Antriebsart3="Vollelektrisch (BEV)"),AND(COUNT(G16,G18:G20)&lt;4,Antriebsart3="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="389">
+      <c r="H28" s="388">
         <f>IF(OR(AND(COUNT(H16:H22)&lt;7,Antriebsart4="Plug-In-Hybrid (PHEV)"),AND(COUNT(H17,H22)&lt;2,Antriebsart4="Vollelektrisch (BEV)"),AND(COUNT(H16,H18:H20)&lt;4,Antriebsart4="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="389">
+      <c r="I28" s="388">
         <f>IF(OR(AND(COUNT(I16:I22)&lt;7,Antriebsart5="Plug-In-Hybrid (PHEV)"),AND(COUNT(I17,I22)&lt;2,Antriebsart5="Vollelektrisch (BEV)"),AND(COUNT(I16,I18:I20)&lt;4,Antriebsart5="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
@@ -19806,33 +19803,33 @@
       <c r="R28" s="7"/>
     </row>
     <row r="29" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="426" t="s">
+      <c r="E29" s="425" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="427"/>
-      <c r="G29" s="427"/>
-      <c r="H29" s="427"/>
-      <c r="I29" s="428"/>
+      <c r="F29" s="426"/>
+      <c r="G29" s="426"/>
+      <c r="H29" s="426"/>
+      <c r="I29" s="427"/>
     </row>
     <row r="30" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="421" t="s">
+      <c r="E30" s="420" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="408"/>
-      <c r="G30" s="408"/>
-      <c r="H30" s="408"/>
-      <c r="I30" s="422"/>
+      <c r="F30" s="407"/>
+      <c r="G30" s="407"/>
+      <c r="H30" s="407"/>
+      <c r="I30" s="421"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="E31" s="423"/>
-      <c r="F31" s="424"/>
-      <c r="G31" s="424"/>
-      <c r="H31" s="424"/>
-      <c r="I31" s="425"/>
+      <c r="E31" s="422"/>
+      <c r="F31" s="423"/>
+      <c r="G31" s="423"/>
+      <c r="H31" s="423"/>
+      <c r="I31" s="424"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -20225,7 +20222,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20239,7 +20236,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20282,37 +20279,37 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="C6" s="439" t="str">
+        <v>433</v>
+      </c>
+      <c r="C6" s="438" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v/>
       </c>
-      <c r="D6" s="440"/>
-      <c r="E6" s="440"/>
-      <c r="F6" s="440"/>
-      <c r="G6" s="440"/>
-      <c r="H6" s="441"/>
+      <c r="D6" s="439"/>
+      <c r="E6" s="439"/>
+      <c r="F6" s="439"/>
+      <c r="G6" s="439"/>
+      <c r="H6" s="440"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="442"/>
-      <c r="D7" s="443"/>
-      <c r="E7" s="443"/>
-      <c r="F7" s="443"/>
-      <c r="G7" s="443"/>
-      <c r="H7" s="444"/>
+      <c r="C7" s="441"/>
+      <c r="D7" s="442"/>
+      <c r="E7" s="442"/>
+      <c r="F7" s="442"/>
+      <c r="G7" s="442"/>
+      <c r="H7" s="443"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="445"/>
-      <c r="D8" s="446"/>
-      <c r="E8" s="446"/>
-      <c r="F8" s="446"/>
-      <c r="G8" s="446"/>
-      <c r="H8" s="447"/>
+      <c r="C8" s="444"/>
+      <c r="D8" s="445"/>
+      <c r="E8" s="445"/>
+      <c r="F8" s="445"/>
+      <c r="G8" s="445"/>
+      <c r="H8" s="446"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -20349,11 +20346,11 @@
       <c r="B11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="435" t="str">
+      <c r="C11" s="434" t="str">
         <f>IF(Datum=0,"",Datum)</f>
         <v/>
       </c>
-      <c r="D11" s="436"/>
+      <c r="D11" s="435"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -20364,7 +20361,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20403,7 +20400,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
+      <c r="B15" s="292" t="s">
         <v>77</v>
       </c>
       <c r="C15" s="21"/>
@@ -20491,10 +20488,10 @@
       <c r="I18" s="107"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="321" t="s">
+      <c r="A19" s="320" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="338" t="str">
+      <c r="B19" s="337" t="str">
         <f>IF(FinArt="Kauf",KaufpreisRech,"Fahrzeugkosten (Leasingrate/Miete)")</f>
         <v>Fahrzeugkosten (Leasingrate/Miete)</v>
       </c>
@@ -20517,13 +20514,13 @@
         <f>Erg.Fzg._4!$C$54+Erg.Fzg._4!$C$55</f>
         <v>0</v>
       </c>
-      <c r="H19" s="337">
+      <c r="H19" s="336">
         <f>Erg.Fzg._5!$C$54+Erg.Fzg._5!$C$55</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="336"/>
+      <c r="A20" s="335"/>
       <c r="B20" s="45" t="s">
         <v>79</v>
       </c>
@@ -20552,7 +20549,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="437" t="s">
+      <c r="A21" s="436" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="27" t="s">
@@ -20583,7 +20580,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="437"/>
+      <c r="A22" s="436"/>
       <c r="B22" s="27" t="s">
         <v>81</v>
       </c>
@@ -20613,26 +20610,26 @@
       <c r="I22" s="107"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="438"/>
+      <c r="A23" s="437"/>
       <c r="B23" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="325" t="s">
+      <c r="C23" s="324" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="326" t="e">
+      <c r="D23" s="325" t="e">
         <f>Erg.Fzg._1!$C$59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E23" s="326" t="e">
+      <c r="E23" s="325" t="e">
         <f>Erg.Fzg._2!$C$59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F23" s="326" t="e">
+      <c r="F23" s="325" t="e">
         <f>Erg.Fzg._3!$C$59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G23" s="326" t="e">
+      <c r="G23" s="325" t="e">
         <f>Erg.Fzg._4!$C$59</f>
         <v>#DIV/0!</v>
       </c>
@@ -20642,30 +20639,30 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="437" t="s">
+      <c r="A24" s="436" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="332" t="str">
+      <c r="B24" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C24" s="323" t="str">
+      <c r="C24" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D24" s="324" t="str">
+      <c r="D24" s="323" t="str">
         <f>Erg.Fzg._1!$C$60</f>
         <v/>
       </c>
-      <c r="E24" s="324" t="str">
+      <c r="E24" s="323" t="str">
         <f>Erg.Fzg._2!$C$60</f>
         <v/>
       </c>
-      <c r="F24" s="324" t="str">
+      <c r="F24" s="323" t="str">
         <f>Erg.Fzg._3!$C$60</f>
         <v/>
       </c>
-      <c r="G24" s="324" t="str">
+      <c r="G24" s="323" t="str">
         <f>Erg.Fzg._4!$C$60</f>
         <v/>
       </c>
@@ -20675,28 +20672,28 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="437"/>
-      <c r="B25" s="332" t="str">
+      <c r="A25" s="436"/>
+      <c r="B25" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C25" s="323" t="str">
+      <c r="C25" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D25" s="324" t="str">
+      <c r="D25" s="323" t="str">
         <f>Erg.Fzg._1!$C$61</f>
         <v/>
       </c>
-      <c r="E25" s="324" t="str">
+      <c r="E25" s="323" t="str">
         <f>Erg.Fzg._2!$C$61</f>
         <v/>
       </c>
-      <c r="F25" s="324" t="str">
+      <c r="F25" s="323" t="str">
         <f>Erg.Fzg._3!$C$61</f>
         <v/>
       </c>
-      <c r="G25" s="324" t="str">
+      <c r="G25" s="323" t="str">
         <f>Erg.Fzg._4!$C$61</f>
         <v/>
       </c>
@@ -20707,28 +20704,28 @@
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="437"/>
-      <c r="B26" s="332" t="str">
+      <c r="A26" s="436"/>
+      <c r="B26" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C26" s="323" t="str">
+      <c r="C26" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="323" t="str">
         <f>Erg.Fzg._1!$C$62</f>
         <v/>
       </c>
-      <c r="E26" s="324" t="str">
+      <c r="E26" s="323" t="str">
         <f>Erg.Fzg._2!$C$62</f>
         <v/>
       </c>
-      <c r="F26" s="324" t="str">
+      <c r="F26" s="323" t="str">
         <f>Erg.Fzg._3!$C$62</f>
         <v/>
       </c>
-      <c r="G26" s="324" t="str">
+      <c r="G26" s="323" t="str">
         <f>Erg.Fzg._4!$C$62</f>
         <v/>
       </c>
@@ -20832,92 +20829,92 @@
       <c r="B30" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="316" t="s">
+      <c r="C30" s="315" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="314" t="e">
+      <c r="D30" s="313" t="e">
         <f>Erg.Fzg._1!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E30" s="314" t="e">
+      <c r="E30" s="313" t="e">
         <f>Erg.Fzg._2!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F30" s="314" t="e">
+      <c r="F30" s="313" t="e">
         <f>Erg.Fzg._3!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G30" s="314" t="e">
+      <c r="G30" s="313" t="e">
         <f>Erg.Fzg._4!$C$65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="315" t="e">
+      <c r="H30" s="314" t="e">
         <f>Erg.Fzg._5!$C$65</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="309"/>
+      <c r="A31" s="308"/>
       <c r="B31" s="98" t="s">
-        <v>444</v>
-      </c>
-      <c r="C31" s="317" t="s">
+        <v>443</v>
+      </c>
+      <c r="C31" s="316" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="318">
+      <c r="D31" s="317">
         <f>Erg.Fzg._1!$C$66</f>
         <v>0</v>
       </c>
-      <c r="E31" s="318">
+      <c r="E31" s="317">
         <f>Erg.Fzg._2!$C$66</f>
         <v>0</v>
       </c>
-      <c r="F31" s="318">
+      <c r="F31" s="317">
         <f>Erg.Fzg._3!$C$66</f>
         <v>0</v>
       </c>
-      <c r="G31" s="318">
+      <c r="G31" s="317">
         <f>Erg.Fzg._4!$C$66</f>
         <v>0</v>
       </c>
-      <c r="H31" s="319">
+      <c r="H31" s="318">
         <f>Erg.Fzg._5!$C$66</f>
         <v>0</v>
       </c>
       <c r="I31" s="91"/>
     </row>
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="309"/>
-      <c r="B32" s="310" t="s">
-        <v>433</v>
-      </c>
-      <c r="C32" s="311" t="s">
+      <c r="A32" s="308"/>
+      <c r="B32" s="309" t="s">
         <v>432</v>
       </c>
-      <c r="D32" s="312" t="e">
+      <c r="C32" s="310" t="s">
+        <v>431</v>
+      </c>
+      <c r="D32" s="311" t="e">
         <f>SUM(D30:D31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="312" t="e">
+      <c r="E32" s="311" t="e">
         <f t="shared" ref="E32:H32" si="2">SUM(E30:E31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F32" s="312" t="e">
+      <c r="F32" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G32" s="312" t="e">
+      <c r="G32" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="313" t="e">
+      <c r="H32" s="312" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="91"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="293" t="s">
+      <c r="B34" s="292" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="21"/>
@@ -21049,7 +21046,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -21059,11 +21056,11 @@
       <c r="H1" s="119"/>
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="320" t="s">
+      <c r="A2" s="319" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -21106,37 +21103,37 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="C6" s="439" t="str">
+        <v>433</v>
+      </c>
+      <c r="C6" s="438" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v/>
       </c>
-      <c r="D6" s="440"/>
-      <c r="E6" s="440"/>
-      <c r="F6" s="440"/>
-      <c r="G6" s="440"/>
-      <c r="H6" s="441"/>
+      <c r="D6" s="439"/>
+      <c r="E6" s="439"/>
+      <c r="F6" s="439"/>
+      <c r="G6" s="439"/>
+      <c r="H6" s="440"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="442"/>
-      <c r="D7" s="443"/>
-      <c r="E7" s="443"/>
-      <c r="F7" s="443"/>
-      <c r="G7" s="443"/>
-      <c r="H7" s="444"/>
+      <c r="C7" s="441"/>
+      <c r="D7" s="442"/>
+      <c r="E7" s="442"/>
+      <c r="F7" s="442"/>
+      <c r="G7" s="442"/>
+      <c r="H7" s="443"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="445"/>
-      <c r="D8" s="446"/>
-      <c r="E8" s="446"/>
-      <c r="F8" s="446"/>
-      <c r="G8" s="446"/>
-      <c r="H8" s="447"/>
+      <c r="C8" s="444"/>
+      <c r="D8" s="445"/>
+      <c r="E8" s="445"/>
+      <c r="F8" s="445"/>
+      <c r="G8" s="445"/>
+      <c r="H8" s="446"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -21173,11 +21170,11 @@
       <c r="B11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="435" t="str">
+      <c r="C11" s="434" t="str">
         <f>IF(Datum=0,"",Datum)</f>
         <v/>
       </c>
-      <c r="D11" s="436"/>
+      <c r="D11" s="435"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -21188,7 +21185,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21227,8 +21224,8 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
-        <v>424</v>
+      <c r="B15" s="292" t="s">
+        <v>423</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21285,7 +21282,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="437" t="s">
+      <c r="A18" s="436" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="27" t="s">
@@ -21316,7 +21313,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="437"/>
+      <c r="A19" s="436"/>
       <c r="B19" s="27" t="s">
         <v>90</v>
       </c>
@@ -21345,7 +21342,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="437"/>
+      <c r="A20" s="436"/>
       <c r="B20" s="27" t="s">
         <v>81</v>
       </c>
@@ -21375,7 +21372,7 @@
       <c r="I20" s="107"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="437"/>
+      <c r="A21" s="436"/>
       <c r="B21" s="29" t="s">
         <v>82</v>
       </c>
@@ -21525,7 +21522,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>87</v>
@@ -21554,37 +21551,37 @@
     </row>
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
-      <c r="B27" s="310" t="s">
-        <v>433</v>
-      </c>
-      <c r="C27" s="311" t="s">
+      <c r="B27" s="309" t="s">
         <v>432</v>
       </c>
-      <c r="D27" s="312" t="e">
+      <c r="C27" s="310" t="s">
+        <v>431</v>
+      </c>
+      <c r="D27" s="311" t="e">
         <f>SUM(D25:D26)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="312" t="e">
+      <c r="E27" s="311" t="e">
         <f t="shared" ref="E27:G27" si="2">SUM(E25:E26)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F27" s="312" t="e">
+      <c r="F27" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G27" s="312" t="e">
+      <c r="G27" s="311" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="313" t="e">
+      <c r="H27" s="312" t="e">
         <f>SUM(H25:H26)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="91"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="293" t="s">
-        <v>425</v>
+      <c r="B29" s="292" t="s">
+        <v>424</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21751,20 +21748,20 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
-      <c r="B4" s="293" t="s">
+      <c r="B4" s="292" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="354"/>
-      <c r="D4" s="354"/>
-      <c r="E4" s="354"/>
-      <c r="F4" s="354"/>
-      <c r="G4" s="354"/>
-      <c r="H4" s="355"/>
+      <c r="C4" s="353"/>
+      <c r="D4" s="353"/>
+      <c r="E4" s="353"/>
+      <c r="F4" s="353"/>
+      <c r="G4" s="353"/>
+      <c r="H4" s="354"/>
       <c r="I4" s="190"/>
       <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="391" t="s">
+      <c r="A5" s="390" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="219"/>
@@ -21776,14 +21773,14 @@
       <c r="H5" s="219"/>
       <c r="I5" s="190"/>
       <c r="J5" s="119"/>
-      <c r="L5" s="467" t="s">
+      <c r="L5" s="466" t="s">
         <v>398</v>
       </c>
-      <c r="M5" s="467"/>
-      <c r="N5" s="467"/>
+      <c r="M5" s="466"/>
+      <c r="N5" s="466"/>
     </row>
     <row r="6" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="391"/>
+      <c r="A6" s="390"/>
       <c r="B6" s="220" t="s">
         <v>93</v>
       </c>
@@ -21791,10 +21788,10 @@
         <v>42</v>
       </c>
       <c r="D6" s="221" t="s">
+        <v>508</v>
+      </c>
+      <c r="E6" s="221" t="s">
         <v>509</v>
-      </c>
-      <c r="E6" s="221" t="s">
-        <v>510</v>
       </c>
       <c r="F6" s="221" t="s">
         <v>94</v>
@@ -21805,511 +21802,511 @@
       <c r="H6" s="221" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="306" t="s">
+      <c r="I6" s="305" t="s">
         <v>97</v>
       </c>
       <c r="J6" s="119"/>
-      <c r="L6" s="467"/>
-      <c r="M6" s="467"/>
-      <c r="N6" s="467"/>
+      <c r="L6" s="466"/>
+      <c r="M6" s="466"/>
+      <c r="N6" s="466"/>
     </row>
     <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="352"/>
-      <c r="B7" s="454" t="s">
+      <c r="A7" s="351"/>
+      <c r="B7" s="453" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="460" t="s">
+      <c r="C7" s="459" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="370" t="s">
+      <c r="D7" s="369" t="s">
+        <v>510</v>
+      </c>
+      <c r="E7" s="385" t="s">
         <v>511</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>512</v>
       </c>
       <c r="F7" s="223">
         <v>230</v>
       </c>
-      <c r="G7" s="272"/>
+      <c r="G7" s="271"/>
       <c r="H7" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="307">
+      <c r="I7" s="306">
         <f t="shared" ref="I7:I25" si="0">IF(ISBLANK(G7),F7,G7)</f>
         <v>230</v>
       </c>
       <c r="J7" s="119"/>
-      <c r="L7" s="467"/>
-      <c r="M7" s="467"/>
-      <c r="N7" s="467"/>
+      <c r="L7" s="466"/>
+      <c r="M7" s="466"/>
+      <c r="N7" s="466"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="352"/>
-      <c r="B8" s="455"/>
-      <c r="C8" s="461"/>
-      <c r="D8" s="458" t="s">
-        <v>513</v>
-      </c>
-      <c r="E8" s="387" t="s">
-        <v>562</v>
+      <c r="A8" s="351"/>
+      <c r="B8" s="454"/>
+      <c r="C8" s="460"/>
+      <c r="D8" s="457" t="s">
+        <v>512</v>
+      </c>
+      <c r="E8" s="386" t="s">
+        <v>560</v>
       </c>
       <c r="F8" s="223">
         <v>150</v>
       </c>
-      <c r="G8" s="272"/>
+      <c r="G8" s="271"/>
       <c r="H8" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="307">
+      <c r="I8" s="306">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="J8" s="119"/>
-      <c r="L8" s="467"/>
-      <c r="M8" s="467"/>
-      <c r="N8" s="467"/>
+      <c r="L8" s="466"/>
+      <c r="M8" s="466"/>
+      <c r="N8" s="466"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="352"/>
-      <c r="B9" s="455"/>
-      <c r="C9" s="461"/>
-      <c r="D9" s="458"/>
-      <c r="E9" s="386" t="s">
-        <v>521</v>
+      <c r="A9" s="351"/>
+      <c r="B9" s="454"/>
+      <c r="C9" s="460"/>
+      <c r="D9" s="457"/>
+      <c r="E9" s="385" t="s">
+        <v>519</v>
       </c>
       <c r="F9" s="223">
         <v>160</v>
       </c>
-      <c r="G9" s="272"/>
+      <c r="G9" s="271"/>
       <c r="H9" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="307">
+      <c r="I9" s="306">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="J9" s="119"/>
-      <c r="L9" s="467"/>
-      <c r="M9" s="467"/>
-      <c r="N9" s="467"/>
+      <c r="L9" s="466"/>
+      <c r="M9" s="466"/>
+      <c r="N9" s="466"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="352"/>
-      <c r="B10" s="455"/>
-      <c r="C10" s="461"/>
-      <c r="D10" s="458"/>
-      <c r="E10" s="387" t="s">
-        <v>522</v>
+      <c r="A10" s="351"/>
+      <c r="B10" s="454"/>
+      <c r="C10" s="460"/>
+      <c r="D10" s="457"/>
+      <c r="E10" s="386" t="s">
+        <v>520</v>
       </c>
       <c r="F10" s="223">
         <v>190</v>
       </c>
-      <c r="G10" s="272"/>
+      <c r="G10" s="271"/>
       <c r="H10" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="307">
+      <c r="I10" s="306">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
       <c r="J10" s="119"/>
-      <c r="L10" s="467"/>
-      <c r="M10" s="467"/>
-      <c r="N10" s="467"/>
+      <c r="L10" s="466"/>
+      <c r="M10" s="466"/>
+      <c r="N10" s="466"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="352"/>
-      <c r="B11" s="455"/>
-      <c r="C11" s="462"/>
-      <c r="D11" s="459"/>
-      <c r="E11" s="386" t="s">
-        <v>523</v>
+      <c r="A11" s="351"/>
+      <c r="B11" s="454"/>
+      <c r="C11" s="461"/>
+      <c r="D11" s="458"/>
+      <c r="E11" s="385" t="s">
+        <v>521</v>
       </c>
       <c r="F11" s="223">
         <v>210</v>
       </c>
-      <c r="G11" s="272"/>
+      <c r="G11" s="271"/>
       <c r="H11" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="307">
+      <c r="I11" s="306">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
       <c r="J11" s="119"/>
-      <c r="L11" s="467"/>
-      <c r="M11" s="467"/>
-      <c r="N11" s="467"/>
+      <c r="L11" s="466"/>
+      <c r="M11" s="466"/>
+      <c r="N11" s="466"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="352"/>
-      <c r="B12" s="456"/>
+      <c r="A12" s="351"/>
+      <c r="B12" s="455"/>
       <c r="C12" s="222" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="223" t="s">
-        <v>503</v>
-      </c>
-      <c r="E12" s="386" t="s">
-        <v>503</v>
+        <v>502</v>
+      </c>
+      <c r="E12" s="385" t="s">
+        <v>502</v>
       </c>
       <c r="F12" s="223">
         <v>40</v>
       </c>
-      <c r="G12" s="272"/>
+      <c r="G12" s="271"/>
       <c r="H12" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="307">
+      <c r="I12" s="306">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J12" s="119"/>
-      <c r="L12" s="467"/>
-      <c r="M12" s="467"/>
-      <c r="N12" s="467"/>
+      <c r="L12" s="466"/>
+      <c r="M12" s="466"/>
+      <c r="N12" s="466"/>
     </row>
     <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="352"/>
-      <c r="B13" s="454" t="s">
+      <c r="A13" s="351"/>
+      <c r="B13" s="453" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="460" t="s">
+      <c r="C13" s="459" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="371" t="s">
+      <c r="D13" s="370" t="s">
+        <v>510</v>
+      </c>
+      <c r="E13" s="385" t="s">
         <v>511</v>
-      </c>
-      <c r="E13" s="386" t="s">
-        <v>512</v>
       </c>
       <c r="F13" s="223">
         <v>32</v>
       </c>
-      <c r="G13" s="272"/>
+      <c r="G13" s="271"/>
       <c r="H13" s="222" t="s">
         <v>105</v>
       </c>
-      <c r="I13" s="307">
+      <c r="I13" s="306">
         <f>IF(ISBLANK(G13),F13,G13)</f>
         <v>32</v>
       </c>
       <c r="J13" s="119"/>
-      <c r="L13" s="467"/>
-      <c r="M13" s="467"/>
-      <c r="N13" s="467"/>
+      <c r="L13" s="466"/>
+      <c r="M13" s="466"/>
+      <c r="N13" s="466"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="352"/>
-      <c r="B14" s="455"/>
-      <c r="C14" s="461"/>
-      <c r="D14" s="457" t="s">
-        <v>513</v>
-      </c>
-      <c r="E14" s="386" t="s">
-        <v>562</v>
+      <c r="A14" s="351"/>
+      <c r="B14" s="454"/>
+      <c r="C14" s="460"/>
+      <c r="D14" s="456" t="s">
+        <v>512</v>
+      </c>
+      <c r="E14" s="385" t="s">
+        <v>560</v>
       </c>
       <c r="F14" s="223">
         <v>20</v>
       </c>
-      <c r="G14" s="272"/>
+      <c r="G14" s="271"/>
       <c r="H14" s="222" t="s">
         <v>105</v>
       </c>
-      <c r="I14" s="307">
+      <c r="I14" s="306">
         <f>IF(ISBLANK(G14),F14,G14)</f>
         <v>20</v>
       </c>
       <c r="J14" s="119"/>
-      <c r="L14" s="467"/>
-      <c r="M14" s="467"/>
-      <c r="N14" s="467"/>
+      <c r="L14" s="466"/>
+      <c r="M14" s="466"/>
+      <c r="N14" s="466"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="352"/>
-      <c r="B15" s="455"/>
-      <c r="C15" s="461"/>
-      <c r="D15" s="458"/>
-      <c r="E15" s="386" t="s">
-        <v>521</v>
+      <c r="A15" s="351"/>
+      <c r="B15" s="454"/>
+      <c r="C15" s="460"/>
+      <c r="D15" s="457"/>
+      <c r="E15" s="385" t="s">
+        <v>519</v>
       </c>
       <c r="F15" s="223">
         <v>28</v>
       </c>
-      <c r="G15" s="272"/>
+      <c r="G15" s="271"/>
       <c r="H15" s="222" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="307">
+      <c r="I15" s="306">
         <f t="shared" ref="I15:I16" si="1">IF(ISBLANK(G15),F15,G15)</f>
         <v>28</v>
       </c>
       <c r="J15" s="119"/>
-      <c r="L15" s="467"/>
-      <c r="M15" s="467"/>
-      <c r="N15" s="467"/>
+      <c r="L15" s="466"/>
+      <c r="M15" s="466"/>
+      <c r="N15" s="466"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="352"/>
-      <c r="B16" s="455"/>
-      <c r="C16" s="462"/>
-      <c r="D16" s="459"/>
-      <c r="E16" s="386" t="s">
-        <v>524</v>
+      <c r="A16" s="351"/>
+      <c r="B16" s="454"/>
+      <c r="C16" s="461"/>
+      <c r="D16" s="458"/>
+      <c r="E16" s="385" t="s">
+        <v>522</v>
       </c>
       <c r="F16" s="223">
         <v>32</v>
       </c>
-      <c r="G16" s="272"/>
+      <c r="G16" s="271"/>
       <c r="H16" s="222" t="s">
         <v>105</v>
       </c>
-      <c r="I16" s="307">
+      <c r="I16" s="306">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="J16" s="119"/>
-      <c r="L16" s="467"/>
-      <c r="M16" s="467"/>
-      <c r="N16" s="467"/>
+      <c r="L16" s="466"/>
+      <c r="M16" s="466"/>
+      <c r="N16" s="466"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="437" t="s">
+      <c r="A17" s="436" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="455"/>
+      <c r="B17" s="454"/>
       <c r="C17" s="222" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E17" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>503</v>
-      </c>
-      <c r="G17" s="272"/>
+        <v>502</v>
+      </c>
+      <c r="G17" s="271"/>
       <c r="H17" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="307" t="str">
+      <c r="I17" s="306" t="str">
         <f>IF(ISBLANK(G17),"keine",G17)</f>
         <v>keine</v>
       </c>
       <c r="J17" s="119"/>
-      <c r="L17" s="467"/>
-      <c r="M17" s="467"/>
-      <c r="N17" s="467"/>
+      <c r="L17" s="466"/>
+      <c r="M17" s="466"/>
+      <c r="N17" s="466"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="437"/>
-      <c r="B18" s="455"/>
+      <c r="A18" s="436"/>
+      <c r="B18" s="454"/>
       <c r="C18" s="222" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D18" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E18" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F18" s="223" t="s">
-        <v>503</v>
-      </c>
-      <c r="G18" s="272"/>
+        <v>502</v>
+      </c>
+      <c r="G18" s="271"/>
       <c r="H18" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="307" t="str">
+      <c r="I18" s="306" t="str">
         <f>IF(ISBLANK(G18),"keine",G18)</f>
         <v>keine</v>
       </c>
       <c r="J18" s="119"/>
-      <c r="L18" s="467"/>
-      <c r="M18" s="467"/>
-      <c r="N18" s="467"/>
+      <c r="L18" s="466"/>
+      <c r="M18" s="466"/>
+      <c r="N18" s="466"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="437"/>
-      <c r="B19" s="456"/>
+      <c r="A19" s="436"/>
+      <c r="B19" s="455"/>
       <c r="C19" s="222" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D19" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E19" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F19" s="223" t="s">
-        <v>503</v>
-      </c>
-      <c r="G19" s="272"/>
+        <v>502</v>
+      </c>
+      <c r="G19" s="271"/>
       <c r="H19" s="222" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="307" t="str">
+      <c r="I19" s="306" t="str">
         <f>IF(ISBLANK(G19),"keine",G19)</f>
         <v>keine</v>
       </c>
       <c r="J19" s="119"/>
-      <c r="L19" s="467"/>
-      <c r="M19" s="467"/>
-      <c r="N19" s="467"/>
+      <c r="L19" s="466"/>
+      <c r="M19" s="466"/>
+      <c r="N19" s="466"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="352"/>
-      <c r="B20" s="378"/>
-      <c r="C20" s="380"/>
-      <c r="D20" s="463" t="s">
-        <v>517</v>
-      </c>
-      <c r="E20" s="464"/>
-      <c r="F20" s="381"/>
-      <c r="G20" s="382"/>
-      <c r="H20" s="379"/>
-      <c r="I20" s="307"/>
+      <c r="A20" s="351"/>
+      <c r="B20" s="377"/>
+      <c r="C20" s="379"/>
+      <c r="D20" s="462" t="s">
+        <v>516</v>
+      </c>
+      <c r="E20" s="463"/>
+      <c r="F20" s="380"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="378"/>
+      <c r="I20" s="306"/>
       <c r="J20" s="119"/>
-      <c r="L20" s="467"/>
-      <c r="M20" s="467"/>
-      <c r="N20" s="467"/>
+      <c r="L20" s="466"/>
+      <c r="M20" s="466"/>
+      <c r="N20" s="466"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="352"/>
-      <c r="B21" s="454" t="s">
+      <c r="A21" s="351"/>
+      <c r="B21" s="453" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="460" t="s">
+      <c r="C21" s="459" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="465" t="s">
-        <v>514</v>
-      </c>
-      <c r="E21" s="466"/>
-      <c r="F21" s="386">
+      <c r="D21" s="464" t="s">
+        <v>513</v>
+      </c>
+      <c r="E21" s="465"/>
+      <c r="F21" s="385">
         <v>64</v>
       </c>
-      <c r="G21" s="272"/>
+      <c r="G21" s="271"/>
       <c r="H21" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="307">
+      <c r="I21" s="306">
         <f>IF(ISBLANK(G21),F21,G21)</f>
         <v>64</v>
       </c>
       <c r="J21" s="119"/>
-      <c r="L21" s="467"/>
-      <c r="M21" s="467"/>
-      <c r="N21" s="467"/>
+      <c r="L21" s="466"/>
+      <c r="M21" s="466"/>
+      <c r="N21" s="466"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="352"/>
-      <c r="B22" s="455"/>
-      <c r="C22" s="461"/>
-      <c r="D22" s="465" t="s">
-        <v>515</v>
-      </c>
-      <c r="E22" s="466"/>
-      <c r="F22" s="386">
+      <c r="A22" s="351"/>
+      <c r="B22" s="454"/>
+      <c r="C22" s="460"/>
+      <c r="D22" s="464" t="s">
+        <v>514</v>
+      </c>
+      <c r="E22" s="465"/>
+      <c r="F22" s="385">
         <v>84</v>
       </c>
-      <c r="G22" s="272"/>
+      <c r="G22" s="271"/>
       <c r="H22" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="307">
+      <c r="I22" s="306">
         <f t="shared" ref="I22:I23" si="2">IF(ISBLANK(G22),F22,G22)</f>
         <v>84</v>
       </c>
       <c r="J22" s="119"/>
-      <c r="K22" s="383"/>
-      <c r="L22" s="467"/>
-      <c r="M22" s="467"/>
-      <c r="N22" s="467"/>
+      <c r="K22" s="382"/>
+      <c r="L22" s="466"/>
+      <c r="M22" s="466"/>
+      <c r="N22" s="466"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="352"/>
-      <c r="B23" s="456"/>
-      <c r="C23" s="462"/>
-      <c r="D23" s="465" t="s">
-        <v>516</v>
-      </c>
-      <c r="E23" s="466"/>
-      <c r="F23" s="386">
+      <c r="A23" s="351"/>
+      <c r="B23" s="455"/>
+      <c r="C23" s="461"/>
+      <c r="D23" s="464" t="s">
+        <v>515</v>
+      </c>
+      <c r="E23" s="465"/>
+      <c r="F23" s="385">
         <v>100</v>
       </c>
-      <c r="G23" s="272"/>
+      <c r="G23" s="271"/>
       <c r="H23" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="I23" s="307">
+      <c r="I23" s="306">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="J23" s="119"/>
-      <c r="L23" s="467"/>
-      <c r="M23" s="467"/>
-      <c r="N23" s="467"/>
+      <c r="L23" s="466"/>
+      <c r="M23" s="466"/>
+      <c r="N23" s="466"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="352"/>
-      <c r="B24" s="367" t="s">
+      <c r="A24" s="351"/>
+      <c r="B24" s="366" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="369" t="s">
+      <c r="C24" s="368" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="465" t="s">
-        <v>518</v>
-      </c>
-      <c r="E24" s="466"/>
-      <c r="F24" s="388">
+      <c r="D24" s="464" t="s">
+        <v>517</v>
+      </c>
+      <c r="E24" s="465"/>
+      <c r="F24" s="387">
         <v>3.6</v>
       </c>
-      <c r="G24" s="272"/>
+      <c r="G24" s="271"/>
       <c r="H24" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="I24" s="307">
+      <c r="I24" s="306">
         <f>IF(ISBLANK(G24),F24,G24)</f>
         <v>3.6</v>
       </c>
       <c r="J24" s="119"/>
-      <c r="L24" s="467"/>
-      <c r="M24" s="467"/>
-      <c r="N24" s="467"/>
+      <c r="L24" s="466"/>
+      <c r="M24" s="466"/>
+      <c r="N24" s="466"/>
     </row>
     <row r="25" spans="1:14" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="353"/>
-      <c r="B25" s="356" t="s">
+      <c r="A25" s="352"/>
+      <c r="B25" s="355" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="225" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E25" s="223" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F25" s="224">
         <v>60</v>
       </c>
-      <c r="G25" s="273"/>
+      <c r="G25" s="272"/>
       <c r="H25" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="307">
+      <c r="I25" s="306">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J25" s="191"/>
-      <c r="L25" s="467"/>
-      <c r="M25" s="467"/>
-      <c r="N25" s="467"/>
+      <c r="L25" s="466"/>
+      <c r="M25" s="466"/>
+      <c r="N25" s="466"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="119"/>
@@ -22367,15 +22364,15 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="196"/>
-      <c r="B31" s="293" t="s">
+      <c r="B31" s="292" t="s">
         <v>394</v>
       </c>
-      <c r="C31" s="339"/>
-      <c r="D31" s="339"/>
-      <c r="E31" s="339"/>
-      <c r="F31" s="340"/>
-      <c r="G31" s="340"/>
-      <c r="H31" s="341"/>
+      <c r="C31" s="338"/>
+      <c r="D31" s="338"/>
+      <c r="E31" s="338"/>
+      <c r="F31" s="339"/>
+      <c r="G31" s="339"/>
+      <c r="H31" s="340"/>
       <c r="I31" s="194"/>
       <c r="J31" s="195"/>
       <c r="K31" s="195"/>
@@ -22383,11 +22380,11 @@
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="196"/>
       <c r="B32" s="6"/>
-      <c r="C32" s="327"/>
-      <c r="D32" s="327"/>
-      <c r="E32" s="327"/>
+      <c r="C32" s="326"/>
+      <c r="D32" s="326"/>
+      <c r="E32" s="326"/>
       <c r="F32" s="6"/>
-      <c r="G32" s="327"/>
+      <c r="G32" s="326"/>
       <c r="H32" s="208"/>
       <c r="I32" s="194"/>
       <c r="J32" s="195"/>
@@ -22395,17 +22392,17 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="196"/>
-      <c r="B33" s="346" t="s">
+      <c r="B33" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="327"/>
-      <c r="D33" s="327"/>
-      <c r="E33" s="327"/>
-      <c r="F33" s="296" t="s">
+      <c r="C33" s="326"/>
+      <c r="D33" s="326"/>
+      <c r="E33" s="326"/>
+      <c r="F33" s="295" t="s">
         <v>109</v>
       </c>
-      <c r="G33" s="347"/>
-      <c r="H33" s="295" t="s">
+      <c r="G33" s="346"/>
+      <c r="H33" s="294" t="s">
         <v>96</v>
       </c>
       <c r="I33" s="194"/>
@@ -22415,15 +22412,15 @@
     <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="196"/>
       <c r="B34" s="6"/>
-      <c r="C34" s="327"/>
-      <c r="D34" s="327"/>
-      <c r="E34" s="327"/>
+      <c r="C34" s="326"/>
+      <c r="D34" s="326"/>
+      <c r="E34" s="326"/>
       <c r="F34" s="209"/>
       <c r="G34" s="210" t="s">
         <v>95</v>
       </c>
-      <c r="H34" s="294"/>
-      <c r="I34" s="308" t="s">
+      <c r="H34" s="293"/>
+      <c r="I34" s="307" t="s">
         <v>110</v>
       </c>
       <c r="J34" s="198" t="s">
@@ -22438,8 +22435,8 @@
       <c r="B35" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="C35" s="372"/>
-      <c r="D35" s="375"/>
+      <c r="C35" s="371"/>
+      <c r="D35" s="374"/>
       <c r="E35" s="213"/>
       <c r="F35" s="214">
         <v>41.4</v>
@@ -22448,12 +22445,12 @@
       <c r="H35" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I35" s="308">
+      <c r="I35" s="307">
         <f>IF(ISNUMBER(G35),G35,F35)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="J35" s="199" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K35" s="254"/>
     </row>
@@ -22462,8 +22459,8 @@
       <c r="B36" s="215" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="373"/>
-      <c r="D36" s="376"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="375"/>
       <c r="E36" s="211"/>
       <c r="F36" s="214">
         <v>59</v>
@@ -22472,12 +22469,12 @@
       <c r="H36" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I36" s="308">
+      <c r="I36" s="307">
         <f>IF(ISNUMBER(G36),G36,F36)/100</f>
         <v>0.59</v>
       </c>
       <c r="J36" s="199" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K36" s="254"/>
     </row>
@@ -22486,13 +22483,13 @@
       <c r="B37" s="216" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="349"/>
-      <c r="G37" s="350"/>
+      <c r="C37" s="373"/>
+      <c r="D37" s="376"/>
+      <c r="E37" s="347"/>
+      <c r="F37" s="348"/>
+      <c r="G37" s="349"/>
       <c r="H37" s="208"/>
-      <c r="I37" s="308">
+      <c r="I37" s="307">
         <f>I35*Input_Beschaffung!J32/100+I36*(1-Input_Beschaffung!J32/100)</f>
         <v>0.502</v>
       </c>
@@ -22500,50 +22497,50 @@
       <c r="K37" s="254"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="450"/>
+      <c r="A38" s="449"/>
       <c r="B38" s="212" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="372"/>
-      <c r="D38" s="375"/>
+      <c r="C38" s="371"/>
+      <c r="D38" s="374"/>
       <c r="E38" s="213"/>
-      <c r="F38" s="271">
+      <c r="F38" s="270">
         <v>1.6719999999999999</v>
       </c>
       <c r="G38" s="243"/>
       <c r="H38" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="I38" s="308">
+      <c r="I38" s="307">
         <f t="shared" ref="I38:I40" si="3">IF(ISNUMBER(G38),G38,F38)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="J38" s="199" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K38" s="254"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="450"/>
+      <c r="A39" s="449"/>
       <c r="B39" s="212" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="372"/>
-      <c r="D39" s="375"/>
+      <c r="C39" s="371"/>
+      <c r="D39" s="374"/>
       <c r="E39" s="213"/>
-      <c r="F39" s="271">
+      <c r="F39" s="270">
         <v>1.788</v>
       </c>
       <c r="G39" s="243"/>
       <c r="H39" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="I39" s="308">
+      <c r="I39" s="307">
         <f t="shared" si="3"/>
         <v>1.788</v>
       </c>
       <c r="J39" s="199" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K39" s="254"/>
     </row>
@@ -22552,8 +22549,8 @@
       <c r="B40" s="212" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="372"/>
-      <c r="D40" s="375"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="374"/>
       <c r="E40" s="213"/>
       <c r="F40" s="217">
         <v>1.3</v>
@@ -22562,12 +22559,12 @@
       <c r="H40" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I40" s="308">
+      <c r="I40" s="307">
         <f t="shared" si="3"/>
         <v>1.3</v>
       </c>
       <c r="J40" s="199" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K40" s="254"/>
     </row>
@@ -22599,31 +22596,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="193"/>
-      <c r="B43" s="293" t="s">
+      <c r="B43" s="292" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="339"/>
-      <c r="D43" s="339"/>
-      <c r="E43" s="339"/>
-      <c r="F43" s="340"/>
-      <c r="G43" s="340"/>
-      <c r="H43" s="341"/>
+      <c r="C43" s="338"/>
+      <c r="D43" s="338"/>
+      <c r="E43" s="338"/>
+      <c r="F43" s="339"/>
+      <c r="G43" s="339"/>
+      <c r="H43" s="340"/>
       <c r="I43" s="201"/>
       <c r="J43" s="201"/>
       <c r="K43" s="201"/>
     </row>
     <row r="44" spans="1:11" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="451" t="s">
+      <c r="B44" s="450" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="452"/>
-      <c r="D44" s="452"/>
-      <c r="E44" s="452"/>
-      <c r="F44" s="452"/>
-      <c r="G44" s="452"/>
-      <c r="H44" s="453"/>
-      <c r="I44" s="308" t="s">
+      <c r="C44" s="451"/>
+      <c r="D44" s="451"/>
+      <c r="E44" s="451"/>
+      <c r="F44" s="451"/>
+      <c r="G44" s="451"/>
+      <c r="H44" s="452"/>
+      <c r="I44" s="307" t="s">
         <v>110</v>
       </c>
       <c r="J44" s="202"/>
@@ -22632,17 +22629,17 @@
     <row r="45" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A45" s="193"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="327"/>
-      <c r="D45" s="327"/>
-      <c r="E45" s="327"/>
-      <c r="F45" s="327"/>
-      <c r="G45" s="342" t="s">
+      <c r="C45" s="326"/>
+      <c r="D45" s="326"/>
+      <c r="E45" s="326"/>
+      <c r="F45" s="326"/>
+      <c r="G45" s="341" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="343" t="s">
+      <c r="H45" s="342" t="s">
         <v>96</v>
       </c>
-      <c r="I45" s="308"/>
+      <c r="I45" s="307"/>
       <c r="J45" s="195"/>
       <c r="K45" s="195"/>
     </row>
@@ -22651,9 +22648,9 @@
       <c r="B46" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="327"/>
-      <c r="D46" s="327"/>
-      <c r="E46" s="327"/>
+      <c r="C46" s="326"/>
+      <c r="D46" s="326"/>
+      <c r="E46" s="326"/>
       <c r="F46" s="218">
         <f>IF(KostTHGVorgabe="(Niedrig) 250", 250, 860)</f>
         <v>860</v>
@@ -22662,7 +22659,7 @@
       <c r="H46" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I46" s="308">
+      <c r="I46" s="307">
         <f>IF(ISNUMBER(G46),G46,F46)</f>
         <v>860</v>
       </c>
@@ -22674,13 +22671,13 @@
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="193"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="327"/>
-      <c r="D47" s="327"/>
-      <c r="E47" s="327"/>
-      <c r="F47" s="344"/>
-      <c r="G47" s="344"/>
-      <c r="H47" s="345"/>
-      <c r="I47" s="308"/>
+      <c r="C47" s="326"/>
+      <c r="D47" s="326"/>
+      <c r="E47" s="326"/>
+      <c r="F47" s="343"/>
+      <c r="G47" s="343"/>
+      <c r="H47" s="344"/>
+      <c r="I47" s="307"/>
       <c r="J47" s="195"/>
       <c r="K47" s="195"/>
     </row>
@@ -22689,9 +22686,9 @@
       <c r="B48" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="327"/>
-      <c r="D48" s="327"/>
-      <c r="E48" s="327"/>
+      <c r="C48" s="326"/>
+      <c r="D48" s="326"/>
+      <c r="E48" s="326"/>
       <c r="F48" s="218">
         <v>0.02</v>
       </c>
@@ -22699,7 +22696,7 @@
       <c r="H48" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="I48" s="308">
+      <c r="I48" s="307">
         <f>IF(ISNUMBER(G48),G48,F48)</f>
         <v>0.02</v>
       </c>
@@ -22723,7 +22720,7 @@
       <c r="H49" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="I49" s="308">
+      <c r="I49" s="307">
         <f>IF(ISNUMBER(G49),G49,F49)</f>
         <v>0.15</v>
       </c>
@@ -22741,7 +22738,7 @@
       <c r="F50" s="194"/>
       <c r="G50" s="194"/>
       <c r="H50" s="193"/>
-      <c r="I50" s="308"/>
+      <c r="I50" s="307"/>
       <c r="J50" s="195"/>
       <c r="K50" s="195"/>
     </row>
@@ -22754,33 +22751,33 @@
       <c r="F51" s="193"/>
       <c r="G51" s="193"/>
       <c r="H51" s="193"/>
-      <c r="I51" s="308"/>
+      <c r="I51" s="307"/>
       <c r="J51" s="194"/>
       <c r="K51" s="194"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="193"/>
-      <c r="B52" s="293" t="s">
+      <c r="B52" s="292" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="351"/>
-      <c r="I52" s="308"/>
+      <c r="C52" s="339"/>
+      <c r="D52" s="339"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
+      <c r="G52" s="339"/>
+      <c r="H52" s="350"/>
+      <c r="I52" s="307"/>
       <c r="J52" s="193"/>
       <c r="K52" s="193"/>
     </row>
     <row r="53" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="193"/>
-      <c r="B53" s="448" t="s">
+      <c r="B53" s="447" t="s">
         <v>399</v>
       </c>
-      <c r="C53" s="449"/>
-      <c r="D53" s="368"/>
-      <c r="E53" s="368"/>
+      <c r="C53" s="448"/>
+      <c r="D53" s="367"/>
+      <c r="E53" s="367"/>
       <c r="F53" s="218">
         <v>84</v>
       </c>
@@ -22788,7 +22785,7 @@
       <c r="H53" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="I53" s="308">
+      <c r="I53" s="307">
         <f>IF(ISNUMBER(G53),G53,F53)</f>
         <v>84</v>
       </c>
@@ -22930,7 +22927,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23073,7 +23070,7 @@
       <c r="B18" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -23084,7 +23081,7 @@
       <c r="B19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -23097,7 +23094,7 @@
       <c r="B20" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
@@ -23110,7 +23107,7 @@
       <c r="B21" s="186" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -23118,13 +23115,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -23134,9 +23131,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -23173,7 +23170,7 @@
       <c r="B28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,8,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23186,7 +23183,7 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23198,7 +23195,7 @@
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -23225,7 +23222,7 @@
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -23238,7 +23235,7 @@
       <c r="B34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -23250,7 +23247,7 @@
       <c r="B35" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="279">
+      <c r="C35" s="278">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -23262,7 +23259,7 @@
       <c r="B36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="279">
+      <c r="C36" s="278">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -23274,7 +23271,7 @@
       <c r="B37" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -23299,7 +23296,7 @@
       <c r="B40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -23312,7 +23309,7 @@
       <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -23344,13 +23341,13 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -23361,9 +23358,9 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -23377,7 +23374,7 @@
       <c r="B48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C48" s="279" t="e">
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -23408,7 +23405,7 @@
       <c r="B54" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
@@ -23418,13 +23415,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C55" s="283">
+        <v>430</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -23437,7 +23434,7 @@
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -23450,7 +23447,7 @@
       <c r="B57" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -23463,7 +23460,7 @@
       <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -23473,63 +23470,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="330" t="e">
+      <c r="C59" s="329" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -23539,7 +23536,7 @@
       <c r="B63" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="284" t="e">
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
@@ -23555,7 +23552,7 @@
       <c r="B65" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="285" t="e">
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -23567,7 +23564,7 @@
       <c r="B66" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -23622,7 +23619,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23775,7 +23772,7 @@
       <c r="B18" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -23787,7 +23784,7 @@
       <c r="B19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -23801,7 +23798,7 @@
       <c r="B20" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
@@ -23815,7 +23812,7 @@
       <c r="B21" s="186" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -23824,13 +23821,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -23841,9 +23838,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -23884,7 +23881,7 @@
       <c r="B28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,8,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23898,7 +23895,7 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23912,7 +23909,7 @@
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -23944,7 +23941,7 @@
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -23958,7 +23955,7 @@
       <c r="B34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -23972,7 +23969,7 @@
       <c r="B35" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -23986,7 +23983,7 @@
       <c r="B36" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -24000,7 +23997,7 @@
       <c r="B37" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -24032,7 +24029,7 @@
       <c r="B40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -24046,7 +24043,7 @@
       <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -24089,13 +24086,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -24106,9 +24103,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24122,7 +24119,7 @@
       <c r="B48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C48" s="279" t="e">
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24159,7 +24156,7 @@
       <c r="B54" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
@@ -24170,13 +24167,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C55" s="283">
+        <v>430</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -24190,7 +24187,7 @@
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24203,7 +24200,7 @@
       <c r="B57" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24216,7 +24213,7 @@
       <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24226,63 +24223,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="330" t="e">
+      <c r="C59" s="329" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -24292,7 +24289,7 @@
       <c r="B63" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="284" t="e">
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24314,7 +24311,7 @@
       <c r="B65" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="285" t="e">
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24326,7 +24323,7 @@
       <c r="B66" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24382,7 +24379,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24535,7 +24532,7 @@
       <c r="B18" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -24547,7 +24544,7 @@
       <c r="B19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -24561,7 +24558,7 @@
       <c r="B20" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
@@ -24575,7 +24572,7 @@
       <c r="B21" s="186" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -24584,13 +24581,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -24601,9 +24598,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -24644,7 +24641,7 @@
       <c r="B28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,8,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -24658,7 +24655,7 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -24672,7 +24669,7 @@
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -24704,7 +24701,7 @@
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -24718,7 +24715,7 @@
       <c r="B34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -24732,7 +24729,7 @@
       <c r="B35" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -24746,7 +24743,7 @@
       <c r="B36" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -24760,7 +24757,7 @@
       <c r="B37" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -24792,7 +24789,7 @@
       <c r="B40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -24806,7 +24803,7 @@
       <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -24849,13 +24846,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -24866,9 +24863,9 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281" t="e">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24882,7 +24879,7 @@
       <c r="B48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C48" s="279" t="e">
+      <c r="C48" s="278" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24919,7 +24916,7 @@
       <c r="B54" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
@@ -24930,13 +24927,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C55" s="283">
+        <v>430</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -24950,7 +24947,7 @@
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24963,7 +24960,7 @@
       <c r="B57" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24976,7 +24973,7 @@
       <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24986,63 +24983,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="327" t="s">
+      <c r="B59" s="326" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="328" t="e">
+      <c r="C59" s="327" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D59" s="327" t="s">
+      <c r="D59" s="326" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v/>
       </c>
-      <c r="C60" s="328" t="str">
+      <c r="C60" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v/>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -25052,7 +25049,7 @@
       <c r="B63" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="284" t="e">
+      <c r="C63" s="283" t="e">
         <f>SUM(C54:C62)</f>
         <v>#DIV/0!</v>
       </c>
@@ -25074,7 +25071,7 @@
       <c r="B65" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="285" t="e">
+      <c r="C65" s="284" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -25086,7 +25083,7 @@
       <c r="B66" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -25120,6 +25117,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -25348,27 +25365,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25385,29 +25407,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>